--- a/docs/damping_curve_MRAx5.xlsx
+++ b/docs/damping_curve_MRAx5.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="123">
   <si>
     <t>Astral · LSC Sweep</t>
   </si>
@@ -299,6 +299,117 @@
     <t>Astral · HSC Sweep</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <t>CTM Racing · MRAx5 · Damping Calculator</t>
+  </si>
+  <si>
+    <t>MRA65 / MRA85 · 砂石拉力 · c / C / R 调节与阻尼力计算</t>
+  </si>
+  <si>
+    <t>适用车型</t>
+  </si>
+  <si>
+    <t>当前曲线参数</t>
+  </si>
+  <si>
+    <t>HSbump · 高速增量</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx5 · Valving Parameters</t>
+  </si>
+  <si>
+    <t>MRA65 / MRA65 (Mod) / MRA85 · 砂石拉力系列；黄色单元格为可编辑标定。</t>
+  </si>
+  <si>
+    <t>HSbump · 高速增量</t>
+  </si>
+  <si>
+    <t>LSR · R（MRA65）</t>
+  </si>
+  <si>
+    <t>Adjusters · 调节格数</t>
+  </si>
+  <si>
+    <t>LSC · 全系列</t>
+  </si>
+  <si>
+    <t>HSC · 全系列</t>
+  </si>
+  <si>
+    <t>LSR · MRA65</t>
+  </si>
+  <si>
+    <t>LSR · MRA85</t>
+  </si>
+  <si>
+    <t>Sweep 使用 MRA65 的格数；MRA65 (Mod) 同为 40 格回弹，MRA85 为 60 格，适用车型在计算器选择。</t>
+  </si>
+  <si>
+    <t>Model · 基础阻尼模型</t>
+  </si>
+  <si>
+    <t>理论曲线采用连续分段接续假设；仅计算基础阻尼，不包含气体支撑、弹簧、HBS/HRS 或 LRS/DSV。</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx5 · LSC Sweep · 读取对应 Sweep 页的阀系选择</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx5 · HSC Sweep · 读取对应 Sweep 页的阀系选择</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx5 · LSR Sweep · 读取对应 Sweep 页的阀系选择</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx5 · Full Sweep · 读取对应 Sweep 页的阀系选择</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx5 · LSC Sweep</t>
+  </si>
+  <si>
+    <t>砂石拉力 · Type-A / Type-B 阀系；各页独立选择。</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx5 · HSC Sweep</t>
+  </si>
+  <si>
+    <t>砂石拉力 · Type-A / Type-B 阀系；各页独立选择。</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx5 · LSR Sweep</t>
+  </si>
+  <si>
+    <t>砂石拉力 · Type-A / Type-B 阀系；各页独立选择。</t>
+  </si>
+  <si>
+    <t>CTM Racing · MRAx5 · Full Sweep</t>
+  </si>
+  <si>
+    <t>砂石拉力 · Type-A / Type-B 阀系；各页独立选择。</t>
+  </si>
+  <si>
+    <t>避震器型号</t>
+  </si>
+  <si>
+    <t>MRA65</t>
+  </si>
+  <si>
+    <t>MRA65 / MRA85 / MRA85 (Mod) · 砂石拉力系列；黄色单元格为可编辑标定。</t>
+  </si>
+  <si>
+    <t>LSC · 全系列</t>
+  </si>
+  <si>
+    <t>HSC · 全系列</t>
+  </si>
+  <si>
+    <t>LSR · MRA65 / 8系改型</t>
+  </si>
+  <si>
+    <t>LSR · MRA85</t>
+  </si>
+  <si>
+    <t>MRA65 与 MRA85 (Mod)：40 格回弹；MRA85：60 格。Sweep 采用 40 格标尺，型号在计算器选择。</t>
+  </si>
 </sst>
 </file>
 
@@ -549,7 +660,7 @@
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>Compression</a:t>
+              <a:t>MRAx5 · LSC Sweep</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1639,7 +1750,7 @@
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>Compression</a:t>
+              <a:t>MRAx5 · HSC Sweep</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2719,7 +2830,7 @@
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>Rebound</a:t>
+              <a:t>MRAx5 · LSR Sweep</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3792,7 +3903,7 @@
                 <a:ea typeface="Arial"/>
                 <a:cs typeface="Arial"/>
               </a:rPr>
-              <a:t>Compression (+) / Rebound (−)</a:t>
+              <a:t>MRAx5 · Compression (+) / Rebound (−)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -6124,7 +6235,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="24" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -6167,7 +6278,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="25" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
@@ -6200,10 +6311,10 @@
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -6360,7 +6471,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="20" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="G13" s="20"/>
       <c r="H13" s="20"/>
@@ -6407,7 +6518,7 @@
         <v>56</v>
       </c>
       <c r="C15" s="1">
-        <f>IF(C6="WRC17",Parameters!D26,Parameters!D25)</f>
+        <f>IF(C6="MRA85",Parameters!D26,Parameters!D25)</f>
         <v>40</v>
       </c>
       <c r="D15" s="1"/>
@@ -6437,7 +6548,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="22" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="G16" s="22"/>
       <c r="H16" s="22"/>
@@ -6484,7 +6595,7 @@
         <v>59</v>
       </c>
       <c r="C18" s="1" t="str">
-        <f>IF(AND(OR(C4="Type-A",C4="Type-B"),OR(C6="Rally2",C6="WRC17",C6="Rally1"),COUNT(C7:C10)=4,C7&gt;=-C13,C7&lt;=0,C8&gt;=-C14,C8&lt;=0,C9&gt;=-C15,C9&lt;=0,C10&gt;=0,INT(C7)=C7,INT(C8)=C8,INT(C9)=C9),"OK","检查输入")</f>
+        <f>IF(AND(OR(C4="Type-A",C4="Type-B"),OR(C6="MRA65",C6="MRA85",C6="MRA85 (Mod)"),COUNT(C7:C10)=4,C7&gt;=-C13,C7&lt;=0,C8&gt;=-C14,C8&lt;=0,C9&gt;=-C15,C9&lt;=0,C10&gt;=0,INT(C7)=C7,INT(C8)=C8,INT(C9)=C9),"OK","检查输入")</f>
         <v>OK</v>
       </c>
       <c r="D18" s="1"/>
@@ -6972,7 +7083,7 @@
       <formula1>"Type-A,Type-B"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="C6" xr:uid="{00000000-0002-0000-0500-000001000000}">
-      <formula1>"Rally2,WRC17,Rally1"</formula1>
+      <formula1>"MRA65,MRA85,MRA85 (Mod)"</formula1>
     </dataValidation>
     <dataValidation type="whole" sqref="C7" xr:uid="{00000000-0002-0000-0500-000002000000}">
       <formula1>-24</formula1>
@@ -7026,7 +7137,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="24" t="s">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -7069,7 +7180,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="25" t="s">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
@@ -7790,7 +7901,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="24" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -7833,7 +7944,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="25" t="s">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
@@ -8554,7 +8665,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="24" t="s">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -8597,7 +8708,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="25" t="s">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
@@ -9310,7 +9421,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="24" t="s">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -9353,7 +9464,7 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="25" t="s">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
@@ -10070,7 +10181,7 @@
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="24" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -10089,7 +10200,7 @@
     <row r="3" spans="1:15" ht="23" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="25" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
@@ -10446,7 +10557,7 @@
     <row r="13" spans="1:15" ht="23" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>22</v>
@@ -10553,7 +10664,7 @@
     <row r="16" spans="1:15" ht="23" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>19</v>
@@ -10773,7 +10884,7 @@
     <row r="22" spans="1:15" ht="23" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="20" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="20"/>
@@ -10792,7 +10903,7 @@
     <row r="23" spans="1:15" ht="23" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="22" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="C23" s="22"/>
       <c r="D23" s="1">
@@ -10800,7 +10911,7 @@
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="23" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
@@ -10815,7 +10926,7 @@
     <row r="24" spans="1:15" ht="23" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="22" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="C24" s="22"/>
       <c r="D24" s="1">
@@ -10836,7 +10947,7 @@
     <row r="25" spans="1:15" ht="23" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="22" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="C25" s="22"/>
       <c r="D25" s="1">
@@ -10857,7 +10968,7 @@
     <row r="26" spans="1:15" ht="23" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="22" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="C26" s="22"/>
       <c r="D26" s="1">
@@ -10897,7 +11008,7 @@
     <row r="28" spans="1:15" ht="23" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="20" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="20"/>
@@ -10973,7 +11084,7 @@
     <row r="32" spans="1:15" ht="23" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="19" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
@@ -11191,7 +11302,7 @@
     <row r="1" spans="1:22" ht="22" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="28" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="C1" s="28"/>
       <c r="D1" s="28"/>
@@ -12884,7 +12995,7 @@
     <row r="41" spans="1:22" ht="22" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="28" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="C41" s="28"/>
       <c r="D41" s="28"/>
@@ -14538,7 +14649,7 @@
     </row>
     <row r="81" spans="2:22" ht="22" customHeight="1">
       <c r="B81" s="29" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="C81" s="29"/>
       <c r="D81" s="29"/>
@@ -16191,7 +16302,7 @@
     </row>
     <row r="121" spans="2:22" ht="22" customHeight="1">
       <c r="B121" s="29" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C121" s="29"/>
       <c r="D121" s="29"/>

--- a/docs/damping_curve_MRAx5.xlsx
+++ b/docs/damping_curve_MRAx5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052424E7-9232-490B-BD6E-DAC815AA6112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB9E4E6-A907-40B4-91FE-3B0F5964DBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="6" r:id="rId1"/>
@@ -39,18 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="123">
-  <si>
-    <t>Astral · LSC Sweep</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="90">
   <si>
     <t>Valving</t>
   </si>
   <si>
     <t>Type-A</t>
-  </si>
-  <si>
-    <t>Type-A / Type-B · 切换仅作用于本页。</t>
   </si>
   <si>
     <t>固定 HSC</t>
@@ -68,22 +62,10 @@
     <t>HSC：最软 / 25% / 默认 / 75% / 最硬</t>
   </si>
   <si>
-    <t>Astral · LSR Sweep</t>
-  </si>
-  <si>
     <t>LSR：−40 / −30 / −20 / −10 / 0 R；图中显示回弹力大小。</t>
   </si>
   <si>
-    <t>Astral · Combined Sweep</t>
-  </si>
-  <si>
     <t>压缩与回弹各五条：最软 / 25% / 默认 / 75% / 最硬。</t>
-  </si>
-  <si>
-    <t>Astral · Valving parameters</t>
-  </si>
-  <si>
-    <t>黄色单元格可编辑；Type-A 与 Type-B 分别标定。</t>
   </si>
   <si>
     <t>Type-B</t>
@@ -119,12 +101,6 @@
     <t>倍率</t>
   </si>
   <si>
-    <t>HSbump · 附加梁</t>
-  </si>
-  <si>
-    <t>LSR · R（6 系）</t>
-  </si>
-  <si>
     <t>rebound</t>
   </si>
   <si>
@@ -134,28 +110,7 @@
     <t>HSrebound / rebound</t>
   </si>
   <si>
-    <t>Clicks · 共用调节格数</t>
-  </si>
-  <si>
-    <t>LSC · 所有车型</t>
-  </si>
-  <si>
-    <t>Sweep 以 6 系的 c / C / R 格数显示；计算器支持 WRC17 的 60 格回弹。</t>
-  </si>
-  <si>
-    <t>HSC · 所有车型</t>
-  </si>
-  <si>
-    <t>LSR · Rally2 / Rally1</t>
-  </si>
-  <si>
-    <t>LSR · WRC17</t>
-  </si>
-  <si>
     <t>0 为最硬；负数为从全关退出的格数。</t>
-  </si>
-  <si>
-    <t>Model · 延续当前公式</t>
   </si>
   <si>
     <t>bump2 = bump1 × 中间段倍率；总高速系数 = bump2 + HSbump。</t>
@@ -164,25 +119,10 @@
     <t>回弹力 = rebound × MIN(v, Rebound knee) + HSrebound × MAX(0, v − Rebound knee)。</t>
   </si>
   <si>
-    <t>连续分段接续仍为工作假设；这里计算基础阻尼，不叠加气体、弹簧、HBS/HRS 或 LRS/DSV。</t>
-  </si>
-  <si>
     <t>LSC 只调斜率；Type-A 的 HSC 调第二 knee，Type-B 的 HSC 调第一 knee。</t>
   </si>
   <si>
     <t>研究来源：chatgpt-conversation://6a9ed043-7848-83e8-9d36-6e63c8202898</t>
-  </si>
-  <si>
-    <t>Astral · Damping calculator</t>
-  </si>
-  <si>
-    <t>A / B 独立切换 · 输入实际 c / C / R 格数及轴速</t>
-  </si>
-  <si>
-    <t>车型</t>
-  </si>
-  <si>
-    <t>Rally2</t>
   </si>
   <si>
     <t>当前输入 · 阻尼力大小</t>
@@ -201,9 +141,6 @@
   </si>
   <si>
     <t>c 总格数</t>
-  </si>
-  <si>
-    <t>实际计算参数</t>
   </si>
   <si>
     <t>C 总格数</t>
@@ -225,9 +162,6 @@
   </si>
   <si>
     <t>计算器支持任意非负轴速；Sweep 图维持 0～1 m/s。倍率和膝点由所选阀系插值得到。</t>
-  </si>
-  <si>
-    <t>LSC Sweep · 由本页 Valving 开关选择参数</t>
   </si>
   <si>
     <t>曲线</t>
@@ -272,15 +206,6 @@
     <t>LSR 区间位置</t>
   </si>
   <si>
-    <t>HSC Sweep · 由本页 Valving 开关选择参数</t>
-  </si>
-  <si>
-    <t>LSR Sweep · 由本页 Valving 开关选择参数</t>
-  </si>
-  <si>
-    <t>Full Sweep · 由本页 Valving 开关选择参数</t>
-  </si>
-  <si>
     <t>Calculator · 插值参数</t>
   </si>
   <si>
@@ -296,17 +221,10 @@
     <t>Type-B：第一 knee 由 HSC 控制；第二 knee 固定，统一在 L14 调整。Type-A 调节关系保持原样。</t>
   </si>
   <si>
-    <t>Astral · HSC Sweep</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <t>CTM Racing · MRAx5 · Damping Calculator</t>
   </si>
   <si>
     <t>MRA65 / MRA85 · 砂石拉力 · c / C / R 调节与阻尼力计算</t>
-  </si>
-  <si>
-    <t>适用车型</t>
   </si>
   <si>
     <t>当前曲线参数</t>
@@ -318,9 +236,6 @@
     <t>CTM Racing · MRAx5 · Valving Parameters</t>
   </si>
   <si>
-    <t>MRA65 / MRA65 (Mod) / MRA85 · 砂石拉力系列；黄色单元格为可编辑标定。</t>
-  </si>
-  <si>
     <t>HSbump · 高速增量</t>
   </si>
   <si>
@@ -328,21 +243,6 @@
   </si>
   <si>
     <t>Adjusters · 调节格数</t>
-  </si>
-  <si>
-    <t>LSC · 全系列</t>
-  </si>
-  <si>
-    <t>HSC · 全系列</t>
-  </si>
-  <si>
-    <t>LSR · MRA65</t>
-  </si>
-  <si>
-    <t>LSR · MRA85</t>
-  </si>
-  <si>
-    <t>Sweep 使用 MRA65 的格数；MRA65 (Mod) 同为 40 格回弹，MRA85 为 60 格，适用车型在计算器选择。</t>
   </si>
   <si>
     <t>Model · 基础阻尼模型</t>
@@ -591,22 +491,10 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -615,8 +503,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -826,28 +726,28 @@
                   <c:v>882</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>957.40000000000009</c:v>
+                  <c:v>982.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1032.8</c:v>
+                  <c:v>1082.8</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1108.2</c:v>
+                  <c:v>1183.2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1183.6000000000001</c:v>
+                  <c:v>1283.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1259</c:v>
+                  <c:v>1384</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1334.4</c:v>
+                  <c:v>1484.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1409.8000000000002</c:v>
+                  <c:v>1584.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1485.2</c:v>
+                  <c:v>1685.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1002,28 +902,28 @@
                   <c:v>1164</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1253.8000000000002</c:v>
+                  <c:v>1278.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1343.6</c:v>
+                  <c:v>1393.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1433.4</c:v>
+                  <c:v>1508.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1523.2</c:v>
+                  <c:v>1623.2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1613</c:v>
+                  <c:v>1738</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1702.8000000000002</c:v>
+                  <c:v>1852.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1792.6</c:v>
+                  <c:v>1967.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1882.4</c:v>
+                  <c:v>2082.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1178,28 +1078,28 @@
                   <c:v>1440</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1543</c:v>
+                  <c:v>1568</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1646</c:v>
+                  <c:v>1696</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1749</c:v>
+                  <c:v>1824</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1852</c:v>
+                  <c:v>1952</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1955</c:v>
+                  <c:v>2080</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2058</c:v>
+                  <c:v>2208</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2161</c:v>
+                  <c:v>2336</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2264</c:v>
+                  <c:v>2464</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1354,28 +1254,28 @@
                   <c:v>1710</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1825</c:v>
+                  <c:v>1850</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1940</c:v>
+                  <c:v>1990</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2055</c:v>
+                  <c:v>2130</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2170</c:v>
+                  <c:v>2270</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2285</c:v>
+                  <c:v>2410</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2400</c:v>
+                  <c:v>2550</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2515</c:v>
+                  <c:v>2690</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2630</c:v>
+                  <c:v>2830</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1530,28 +1430,28 @@
                   <c:v>1974</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2099.8000000000002</c:v>
+                  <c:v>2124.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2225.6</c:v>
+                  <c:v>2275.6</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2351.4</c:v>
+                  <c:v>2426.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2477.2000000000003</c:v>
+                  <c:v>2577.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2603</c:v>
+                  <c:v>2728</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2728.8</c:v>
+                  <c:v>2878.8</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2854.6</c:v>
+                  <c:v>3029.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2980.4</c:v>
+                  <c:v>3180.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1870,64 +1770,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>367.5</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>592.5</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>705</c:v>
+                  <c:v>828</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>817.5</c:v>
+                  <c:v>906</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>930.00000000000011</c:v>
+                  <c:v>984</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1042.5</c:v>
+                  <c:v>1062</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1155</c:v>
+                  <c:v>1140</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1267.5</c:v>
+                  <c:v>1218</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1390</c:v>
+                  <c:v>1296</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1527.5</c:v>
+                  <c:v>1424</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1665</c:v>
+                  <c:v>1552</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1802.5</c:v>
+                  <c:v>1680</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1940</c:v>
+                  <c:v>1808</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2077.5</c:v>
+                  <c:v>1936</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2215</c:v>
+                  <c:v>2064</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2352.5</c:v>
+                  <c:v>2192</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2490</c:v>
+                  <c:v>2320</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2046,64 +1946,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>367.5</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>592.5</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>705</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>817.5</c:v>
+                  <c:v>978</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>930.00000000000011</c:v>
+                  <c:v>1056</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1042.5</c:v>
+                  <c:v>1134</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1155</c:v>
+                  <c:v>1212</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1267.5</c:v>
+                  <c:v>1290</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1392.5</c:v>
+                  <c:v>1368</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1567.5</c:v>
+                  <c:v>1496</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1742.5</c:v>
+                  <c:v>1624</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1917.5</c:v>
+                  <c:v>1752</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2092.5</c:v>
+                  <c:v>1880</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2267.5</c:v>
+                  <c:v>2008</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2442.5</c:v>
+                  <c:v>2136</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2617.5</c:v>
+                  <c:v>2264</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2792.5</c:v>
+                  <c:v>2392</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2222,64 +2122,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>367.5</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>592.5</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>705</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>817.5</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>930.00000000000011</c:v>
+                  <c:v>1128</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1042.5</c:v>
+                  <c:v>1206</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1155</c:v>
+                  <c:v>1284</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1267.5</c:v>
+                  <c:v>1362</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1380</c:v>
+                  <c:v>1440</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1592.5</c:v>
+                  <c:v>1568</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1805</c:v>
+                  <c:v>1696</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2017.5</c:v>
+                  <c:v>1824</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2230</c:v>
+                  <c:v>1952</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2442.5</c:v>
+                  <c:v>2080</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2655</c:v>
+                  <c:v>2208</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2867.5</c:v>
+                  <c:v>2336</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3080</c:v>
+                  <c:v>2464</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2398,64 +2298,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>367.5</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>592.5</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>705</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>817.5</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>930.00000000000011</c:v>
+                  <c:v>1200</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1042.5</c:v>
+                  <c:v>1278</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1155</c:v>
+                  <c:v>1356</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1267.5</c:v>
+                  <c:v>1434</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1380</c:v>
+                  <c:v>1512</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1602.5</c:v>
+                  <c:v>1640</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1852.5</c:v>
+                  <c:v>1768</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2102.5</c:v>
+                  <c:v>1896</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2352.5</c:v>
+                  <c:v>2024</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2602.5</c:v>
+                  <c:v>2152</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2852.5</c:v>
+                  <c:v>2280</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3102.5</c:v>
+                  <c:v>2408</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3352.5</c:v>
+                  <c:v>2536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2574,64 +2474,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>367.5</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>592.5</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>705</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>817.5</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>930.00000000000011</c:v>
+                  <c:v>1200</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1042.5</c:v>
+                  <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1155</c:v>
+                  <c:v>1428</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1267.5</c:v>
+                  <c:v>1506</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1380</c:v>
+                  <c:v>1584</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1597.5</c:v>
+                  <c:v>1712</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1885</c:v>
+                  <c:v>1840</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2172.5</c:v>
+                  <c:v>1968</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2460</c:v>
+                  <c:v>2096</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2747.5</c:v>
+                  <c:v>2224</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3035</c:v>
+                  <c:v>2352</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3322.5</c:v>
+                  <c:v>2480</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3610</c:v>
+                  <c:v>2608</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2950,64 +2850,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100</c:v>
+                  <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>150</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>200</c:v>
+                  <c:v>320</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>247.6</c:v>
+                  <c:v>372.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>291.59999999999997</c:v>
+                  <c:v>425.59999999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>335.59999999999997</c:v>
+                  <c:v>478.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>379.6</c:v>
+                  <c:v>531.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>423.6</c:v>
+                  <c:v>584</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>467.6</c:v>
+                  <c:v>636.79999999999995</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>511.60000000000008</c:v>
+                  <c:v>689.6</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>555.6</c:v>
+                  <c:v>742.4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>599.6</c:v>
+                  <c:v>795.2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>643.59999999999991</c:v>
+                  <c:v>847.99999999999989</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>687.6</c:v>
+                  <c:v>900.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>731.60000000000014</c:v>
+                  <c:v>953.60000000000014</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>775.6</c:v>
+                  <c:v>1006.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>819.6</c:v>
+                  <c:v>1059.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>863.6</c:v>
+                  <c:v>1112</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>907.6</c:v>
+                  <c:v>1164.8000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3126,64 +3026,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>75</c:v>
+                  <c:v>102.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>150</c:v>
+                  <c:v>205</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>225</c:v>
+                  <c:v>307.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300</c:v>
+                  <c:v>410</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>375</c:v>
+                  <c:v>493.02499999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>439.2</c:v>
+                  <c:v>556.57499999999993</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>502.2</c:v>
+                  <c:v>620.125</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>565.20000000000005</c:v>
+                  <c:v>683.67499999999995</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>628.20000000000005</c:v>
+                  <c:v>747.22500000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>691.2</c:v>
+                  <c:v>810.77500000000009</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>754.2</c:v>
+                  <c:v>874.32500000000005</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>817.2</c:v>
+                  <c:v>937.875</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>880.2</c:v>
+                  <c:v>1001.4250000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>943.2</c:v>
+                  <c:v>1064.9749999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1006.2000000000002</c:v>
+                  <c:v>1128.5250000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1069.2000000000003</c:v>
+                  <c:v>1192.075</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1132.2</c:v>
+                  <c:v>1255.625</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1195.2000000000003</c:v>
+                  <c:v>1319.1750000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1258.2</c:v>
+                  <c:v>1382.7249999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1321.2000000000003</c:v>
+                  <c:v>1446.2750000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3302,64 +3202,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>200</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>300</c:v>
+                  <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>400</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500</c:v>
+                  <c:v>625</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>591.99999999999989</c:v>
+                  <c:v>697.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>671.99999999999989</c:v>
+                  <c:v>770</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>752</c:v>
+                  <c:v>842.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>832</c:v>
+                  <c:v>915</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>912</c:v>
+                  <c:v>987.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>992</c:v>
+                  <c:v>1060</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1072</c:v>
+                  <c:v>1132.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1152</c:v>
+                  <c:v>1205</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1232</c:v>
+                  <c:v>1277.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1312</c:v>
+                  <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1392</c:v>
+                  <c:v>1422.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1472</c:v>
+                  <c:v>1495</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1552</c:v>
+                  <c:v>1567.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1632</c:v>
+                  <c:v>1640</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1712</c:v>
+                  <c:v>1712.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3478,64 +3378,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>147.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>295</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>375</c:v>
+                  <c:v>442.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>500</c:v>
+                  <c:v>590</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>625</c:v>
+                  <c:v>737.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>750</c:v>
+                  <c:v>851.07500000000005</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>848</c:v>
+                  <c:v>930.72500000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>943</c:v>
+                  <c:v>1010.3750000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1038</c:v>
+                  <c:v>1090.0250000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1133</c:v>
+                  <c:v>1169.6750000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1228</c:v>
+                  <c:v>1249.3250000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1323</c:v>
+                  <c:v>1328.9749999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1418</c:v>
+                  <c:v>1408.625</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1513</c:v>
+                  <c:v>1488.2750000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1608</c:v>
+                  <c:v>1567.9250000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1703</c:v>
+                  <c:v>1647.5750000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1798</c:v>
+                  <c:v>1727.2249999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1893</c:v>
+                  <c:v>1806.875</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1988</c:v>
+                  <c:v>1886.5250000000001</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2083</c:v>
+                  <c:v>1966.1750000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3654,64 +3554,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>340</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>510</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>680</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>850</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>1020</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1033.1999999999998</c:v>
+                  <c:v>1105</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1141.2</c:v>
+                  <c:v>1190</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1249.2</c:v>
+                  <c:v>1275</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1357.2</c:v>
+                  <c:v>1360</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1465.2</c:v>
+                  <c:v>1445</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1573.1999999999998</c:v>
+                  <c:v>1530</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1681.2</c:v>
+                  <c:v>1615</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1789.1999999999998</c:v>
+                  <c:v>1700</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1897.1999999999998</c:v>
+                  <c:v>1785</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2005.2</c:v>
+                  <c:v>1870</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2113.1999999999998</c:v>
+                  <c:v>1955</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2221.1999999999998</c:v>
+                  <c:v>2040</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2329.1999999999998</c:v>
+                  <c:v>2125</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2437.1999999999998</c:v>
+                  <c:v>2210</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4023,64 +3923,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>148.80000000000001</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>196.8</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>244.8</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>292.79999999999995</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>340.79999999999995</c:v>
+                  <c:v>420</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>388.8</c:v>
+                  <c:v>480.00000000000006</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>436.8</c:v>
+                  <c:v>540</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>484.8</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>532.80000000000007</c:v>
+                  <c:v>660.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>590.79999999999995</c:v>
+                  <c:v>736</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>663.8</c:v>
+                  <c:v>836</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>736.8</c:v>
+                  <c:v>936</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>809.8</c:v>
+                  <c:v>1036</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>882.80000000000007</c:v>
+                  <c:v>1136.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>955.8</c:v>
+                  <c:v>1236</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1028.8000000000002</c:v>
+                  <c:v>1336</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1101.8</c:v>
+                  <c:v>1436</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1174.8</c:v>
+                  <c:v>1536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4199,64 +4099,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>87.5</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>175</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>258.82499999999999</c:v>
+                  <c:v>268.64999999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>340.20000000000005</c:v>
+                  <c:v>356.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>421.57500000000005</c:v>
+                  <c:v>444.15</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>502.95</c:v>
+                  <c:v>531.9</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>584.32500000000005</c:v>
+                  <c:v>619.65</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>665.7</c:v>
+                  <c:v>707.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>747.07500000000005</c:v>
+                  <c:v>795.15</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>828.45</c:v>
+                  <c:v>882.9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>909.82500000000005</c:v>
+                  <c:v>970.65000000000009</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1003.6999999999999</c:v>
+                  <c:v>1072.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1147.575</c:v>
+                  <c:v>1230.1500000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1291.4499999999998</c:v>
+                  <c:v>1387.9</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1435.325</c:v>
+                  <c:v>1545.65</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1579.2000000000003</c:v>
+                  <c:v>1703.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1723.075</c:v>
+                  <c:v>1861.1499999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1866.95</c:v>
+                  <c:v>2018.9</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2010.825</c:v>
+                  <c:v>2176.6499999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2154.6999999999998</c:v>
+                  <c:v>2334.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4375,64 +4275,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>125</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>250</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>367.5</c:v>
+                  <c:v>356.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>470.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>592.5</c:v>
+                  <c:v>584.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>705</c:v>
+                  <c:v>698.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>817.5</c:v>
+                  <c:v>812.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>930.00000000000011</c:v>
+                  <c:v>926.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1042.5</c:v>
+                  <c:v>1040.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1155</c:v>
+                  <c:v>1154.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1267.5</c:v>
+                  <c:v>1268.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1380</c:v>
+                  <c:v>1382.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1592.5</c:v>
+                  <c:v>1596.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1805</c:v>
+                  <c:v>1810.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2017.5</c:v>
+                  <c:v>2024.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2230</c:v>
+                  <c:v>2238.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2442.5</c:v>
+                  <c:v>2452.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2655</c:v>
+                  <c:v>2666.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2867.5</c:v>
+                  <c:v>2880.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3080</c:v>
+                  <c:v>3094.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4551,64 +4451,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>162.5</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>325</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>474.82499999999999</c:v>
+                  <c:v>443.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>616.20000000000005</c:v>
+                  <c:v>582</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>757.57500000000005</c:v>
+                  <c:v>720.75</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>898.95</c:v>
+                  <c:v>859.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1040.3249999999998</c:v>
+                  <c:v>998.25</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1181.7</c:v>
+                  <c:v>1137</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1323.075</c:v>
+                  <c:v>1275.75</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1464.45</c:v>
+                  <c:v>1414.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1605.825</c:v>
+                  <c:v>1553.2500000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1747.2</c:v>
+                  <c:v>1692</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1998.575</c:v>
+                  <c:v>1934.75</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2277.4499999999998</c:v>
+                  <c:v>2203.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2556.3249999999998</c:v>
+                  <c:v>2472.25</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2835.2</c:v>
+                  <c:v>2741</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3114.0749999999998</c:v>
+                  <c:v>3009.75</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3392.9500000000003</c:v>
+                  <c:v>3278.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3671.8249999999998</c:v>
+                  <c:v>3547.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3950.7</c:v>
+                  <c:v>3816</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4727,64 +4627,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>200</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>400</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>580.79999999999995</c:v>
+                  <c:v>529.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>748.80000000000007</c:v>
+                  <c:v>691.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>916.8</c:v>
+                  <c:v>853.2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1084.8</c:v>
+                  <c:v>1015.1999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1252.8</c:v>
+                  <c:v>1177.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1420.8000000000002</c:v>
+                  <c:v>1339.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1588.8</c:v>
+                  <c:v>1501.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1756.8</c:v>
+                  <c:v>1663.2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1924.8000000000002</c:v>
+                  <c:v>1825.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2092.8000000000002</c:v>
+                  <c:v>1987.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2365.8000000000002</c:v>
+                  <c:v>2245.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2708.8</c:v>
+                  <c:v>2567.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3051.8</c:v>
+                  <c:v>2889.2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3394.8</c:v>
+                  <c:v>3211.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3737.7999999999997</c:v>
+                  <c:v>3533.2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4080.8</c:v>
+                  <c:v>3855.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4423.7999999999993</c:v>
+                  <c:v>4177.2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4766.8</c:v>
+                  <c:v>4499.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4903,64 +4803,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-50</c:v>
+                  <c:v>-55</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-100</c:v>
+                  <c:v>-110</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-150</c:v>
+                  <c:v>-165</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-200</c:v>
+                  <c:v>-220</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-247.6</c:v>
+                  <c:v>-272.36</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-291.59999999999997</c:v>
+                  <c:v>-320.76</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-335.59999999999997</c:v>
+                  <c:v>-369.15999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-379.6</c:v>
+                  <c:v>-417.56</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-423.6</c:v>
+                  <c:v>-465.96000000000004</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-467.6</c:v>
+                  <c:v>-514.36</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-511.60000000000008</c:v>
+                  <c:v>-562.76</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-555.6</c:v>
+                  <c:v>-611.16</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-599.6</c:v>
+                  <c:v>-659.56000000000006</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-643.59999999999991</c:v>
+                  <c:v>-707.96</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-687.6</c:v>
+                  <c:v>-756.36</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-731.60000000000014</c:v>
+                  <c:v>-804.7600000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-775.6</c:v>
+                  <c:v>-853.16</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-819.6</c:v>
+                  <c:v>-901.56000000000006</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-863.6</c:v>
+                  <c:v>-949.95999999999992</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-907.6</c:v>
+                  <c:v>-998.36</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5079,64 +4979,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-75</c:v>
+                  <c:v>-77.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-150</c:v>
+                  <c:v>-155</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-225</c:v>
+                  <c:v>-232.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-300</c:v>
+                  <c:v>-310</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-375</c:v>
+                  <c:v>-387.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-439.2</c:v>
+                  <c:v>-453.84</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-502.2</c:v>
+                  <c:v>-518.93999999999994</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-565.20000000000005</c:v>
+                  <c:v>-584.04000000000008</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-628.20000000000005</c:v>
+                  <c:v>-649.1400000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-691.2</c:v>
+                  <c:v>-714.24</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-754.2</c:v>
+                  <c:v>-779.34000000000015</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-817.2</c:v>
+                  <c:v>-844.44</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-880.2</c:v>
+                  <c:v>-909.54000000000008</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-943.2</c:v>
+                  <c:v>-974.64</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1006.2000000000002</c:v>
+                  <c:v>-1039.7400000000002</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1069.2000000000003</c:v>
+                  <c:v>-1104.8400000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1132.2</c:v>
+                  <c:v>-1169.94</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1195.2000000000003</c:v>
+                  <c:v>-1235.0400000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1258.2</c:v>
+                  <c:v>-1300.1400000000001</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1321.2000000000003</c:v>
+                  <c:v>-1365.2400000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5431,64 +5331,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-125</c:v>
+                  <c:v>-122.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-250</c:v>
+                  <c:v>-245</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-375</c:v>
+                  <c:v>-367.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-500</c:v>
+                  <c:v>-490</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-625</c:v>
+                  <c:v>-612.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-750</c:v>
+                  <c:v>-735</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-848</c:v>
+                  <c:v>-831.04</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-943</c:v>
+                  <c:v>-924.1400000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1038</c:v>
+                  <c:v>-1017.24</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1133</c:v>
+                  <c:v>-1110.3400000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1228</c:v>
+                  <c:v>-1203.44</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1323</c:v>
+                  <c:v>-1296.54</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1418</c:v>
+                  <c:v>-1389.64</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1513</c:v>
+                  <c:v>-1482.7399999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1608</c:v>
+                  <c:v>-1575.8400000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1703</c:v>
+                  <c:v>-1668.94</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1798</c:v>
+                  <c:v>-1762.04</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1893</c:v>
+                  <c:v>-1855.1399999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1988</c:v>
+                  <c:v>-1948.2399999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2083</c:v>
+                  <c:v>-2041.3400000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5607,64 +5507,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-150</c:v>
+                  <c:v>-145</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-300</c:v>
+                  <c:v>-290</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-450</c:v>
+                  <c:v>-435</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-600</c:v>
+                  <c:v>-580</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-750</c:v>
+                  <c:v>-725</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-900</c:v>
+                  <c:v>-870</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1033.1999999999998</c:v>
+                  <c:v>-998.75999999999988</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1141.2</c:v>
+                  <c:v>-1103.1600000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1249.2</c:v>
+                  <c:v>-1207.56</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1357.2</c:v>
+                  <c:v>-1311.96</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1465.2</c:v>
+                  <c:v>-1416.3600000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1573.1999999999998</c:v>
+                  <c:v>-1520.7599999999998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1681.2</c:v>
+                  <c:v>-1625.1599999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1789.1999999999998</c:v>
+                  <c:v>-1729.56</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1897.1999999999998</c:v>
+                  <c:v>-1833.96</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2005.2</c:v>
+                  <c:v>-1938.3600000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2113.1999999999998</c:v>
+                  <c:v>-2042.76</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2221.1999999999998</c:v>
+                  <c:v>-2147.16</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2329.1999999999998</c:v>
+                  <c:v>-2251.5599999999995</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2437.1999999999998</c:v>
+                  <c:v>-2355.96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6234,20 +6134,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="B2" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -6271,23 +6171,23 @@
     <row r="4" spans="1:15" ht="23" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="E4" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -6311,20 +6211,20 @@
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
+      <c r="F6" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -6334,7 +6234,7 @@
     <row r="7" spans="1:15" ht="23" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3">
         <v>-12</v>
@@ -6355,23 +6255,23 @@
     <row r="8" spans="1:15" ht="23" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3">
         <v>-10</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="27">
+      <c r="F8" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="24">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
-        <v>817.5</v>
-      </c>
-      <c r="J8" s="27"/>
+        <v>1952</v>
+      </c>
+      <c r="J8" s="24"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -6381,7 +6281,7 @@
     <row r="9" spans="1:15" ht="23" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3">
         <v>-20</v>
@@ -6402,23 +6302,23 @@
     <row r="10" spans="1:15" ht="23" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C10" s="16">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="27">
+      <c r="F10" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="24">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
-        <v>671.99999999999989</v>
-      </c>
-      <c r="J10" s="27"/>
+        <v>1422.5</v>
+      </c>
+      <c r="J10" s="24"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -6462,7 +6362,7 @@
     <row r="13" spans="1:15" ht="23" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1">
         <f>Parameters!D23</f>
@@ -6470,13 +6370,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
+      <c r="F13" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -6486,7 +6386,7 @@
     <row r="14" spans="1:15" ht="23" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1">
         <f>Parameters!D24</f>
@@ -6494,17 +6394,17 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
+      <c r="F14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
       <c r="I14" s="18">
         <f>Samples!F165</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -6515,7 +6415,7 @@
     <row r="15" spans="1:15" ht="23" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C15" s="1">
         <f>IF(C6="MRA85",Parameters!D26,Parameters!D25)</f>
@@ -6523,17 +6423,17 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="F15" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="18">
         <f>Samples!I165</f>
-        <v>2250</v>
+        <v>1560</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -6547,17 +6447,17 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
+      <c r="F16" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
       <c r="I16" s="18">
         <f>Samples!J165</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -6571,17 +6471,17 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
+      <c r="F17" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
       <c r="I17" s="18">
         <f>Samples!L165</f>
-        <v>4250</v>
+        <v>2560</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -6592,7 +6492,7 @@
     <row r="18" spans="1:15" ht="23" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C18" s="1" t="str">
         <f>IF(AND(OR(C4="Type-A",C4="Type-B"),OR(C6="MRA65",C6="MRA85",C6="MRA85 (Mod)"),COUNT(C7:C10)=4,C7&gt;=-C13,C7&lt;=0,C8&gt;=-C14,C8&lt;=0,C9&gt;=-C15,C9&lt;=0,C10&gt;=0,INT(C7)=C7,INT(C8)=C8,INT(C9)=C9),"OK","检查输入")</f>
@@ -6617,17 +6517,17 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
+      <c r="F19" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
       <c r="I19" s="18">
         <f>Samples!M165</f>
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -6641,17 +6541,17 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
+      <c r="F20" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="18">
         <f>Samples!P165</f>
-        <v>1600</v>
+        <v>1450</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -6682,17 +6582,17 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
+      <c r="F22" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
       <c r="I22" s="5">
         <f>Samples!G165</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -6706,17 +6606,17 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
+      <c r="F23" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
       <c r="I23" s="5">
         <f>Samples!K165</f>
         <v>0.6</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -6730,17 +6630,17 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
+      <c r="F24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
       <c r="I24" s="5">
         <f>Samples!N165</f>
-        <v>0.28000000000000003</v>
+        <v>0.25</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -6784,20 +6684,20 @@
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
+      <c r="B27" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -7136,20 +7036,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="B2" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -7173,23 +7073,23 @@
     <row r="4" spans="1:15" ht="23" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="E4" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7213,23 +7113,23 @@
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3">
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="E6" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -7813,20 +7713,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="B41" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -7900,20 +7800,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="B2" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -7937,23 +7837,23 @@
     <row r="4" spans="1:15" ht="23" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="E4" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -7977,23 +7877,23 @@
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="3">
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="E6" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -8577,20 +8477,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="B41" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -8664,20 +8564,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="B2" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -8701,23 +8601,23 @@
     <row r="4" spans="1:15" ht="23" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="E4" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8740,20 +8640,20 @@
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="B6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9337,20 +9237,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="B41" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9420,20 +9320,20 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="B2" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
@@ -9457,23 +9357,23 @@
     <row r="4" spans="1:15" ht="23" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>2</v>
-      </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
+      <c r="E4" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9496,20 +9396,20 @@
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
+      <c r="B6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -10093,20 +9993,20 @@
     </row>
     <row r="41" spans="1:15" ht="23" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="B41" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10180,40 +10080,40 @@
     </row>
     <row r="2" spans="1:15" ht="23" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
+      <c r="B2" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="23" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
+      <c r="B3" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="23" customHeight="1">
@@ -10237,30 +10137,30 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
+      <c r="D5" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
+      <c r="J5" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="23" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -10303,10 +10203,10 @@
     <row r="7" spans="1:15" ht="23" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D7" s="1">
         <f>(D$6-1)*$D$23</f>
@@ -10354,10 +10254,10 @@
     <row r="8" spans="1:15" ht="23" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D8" s="1">
         <f>(D$6-1)*$D$24</f>
@@ -10422,27 +10322,27 @@
     <row r="10" spans="1:15" ht="23" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D10" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="E10" s="6">
         <f>(D10+F10)/2</f>
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="F10" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="G10" s="6">
         <f>(F10+H10)/2</f>
-        <v>3250</v>
+        <v>3000</v>
       </c>
       <c r="H10" s="3">
-        <v>4000</v>
+        <v>3600</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="3">
@@ -10467,10 +10367,10 @@
     <row r="11" spans="1:15" ht="23" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D11" s="4">
         <v>0.12</v>
@@ -10512,27 +10412,27 @@
     <row r="12" spans="1:15" ht="23" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D12" s="4">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5">
         <f>(D12+F12)/2</f>
-        <v>0.92999999999999994</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F12" s="4">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="G12" s="5">
         <f>(F12+H12)/2</f>
-        <v>0.87</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="H12" s="4">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="4">
@@ -10557,55 +10457,55 @@
     <row r="13" spans="1:15" ht="23" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D13" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E13" s="6">
         <f>(D13+F13)/2</f>
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="F13" s="3">
         <v>2000</v>
       </c>
       <c r="G13" s="6">
         <f>(F13+H13)/2</f>
-        <v>2750</v>
+        <v>2600</v>
       </c>
       <c r="H13" s="3">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K13" s="6">
         <f>(J13+L13)/2</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L13" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="M13" s="6">
         <f>(L13+N13)/2</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="N13" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="O13" s="1"/>
     </row>
     <row r="14" spans="1:15" ht="23" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D14" s="4">
         <v>0.57999999999999996</v>
@@ -10664,10 +10564,10 @@
     <row r="16" spans="1:15" ht="23" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D16" s="1">
         <f>(D$6-1)*$D$25</f>
@@ -10715,55 +10615,55 @@
     <row r="17" spans="1:15" ht="23" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D17" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E17" s="6">
         <f>(D17+F17)/2</f>
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="F17" s="3">
         <v>2000</v>
       </c>
       <c r="G17" s="6">
         <f>(F17+H17)/2</f>
-        <v>2500</v>
+        <v>2450</v>
       </c>
       <c r="H17" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="K17" s="6">
         <f>(J17+L17)/2</f>
-        <v>2000</v>
+        <v>2050</v>
       </c>
       <c r="L17" s="3">
         <v>2500</v>
       </c>
       <c r="M17" s="6">
         <f>(L17+N17)/2</f>
-        <v>3000</v>
+        <v>2950</v>
       </c>
       <c r="N17" s="3">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="O17" s="1"/>
     </row>
     <row r="18" spans="1:15" ht="23" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D18" s="4">
         <v>0.23</v>
@@ -10805,10 +10705,10 @@
     <row r="19" spans="1:15" ht="23" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D19" s="4">
         <v>0.88</v>
@@ -10883,73 +10783,73 @@
     </row>
     <row r="22" spans="1:15" ht="23" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
+      <c r="B22" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="23" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="C23" s="22"/>
+      <c r="B23" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="20"/>
       <c r="D23" s="1">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
+      <c r="F23" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="23" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" s="22"/>
+      <c r="B24" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="20"/>
       <c r="D24" s="1">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="23" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" s="22"/>
+      <c r="B25" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="20"/>
       <c r="D25" s="1">
         <v>40</v>
       </c>
@@ -10967,25 +10867,25 @@
     </row>
     <row r="26" spans="1:15" ht="23" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="C26" s="22"/>
+      <c r="B26" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="20"/>
       <c r="D26" s="1">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
+      <c r="F26" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="23" customHeight="1">
@@ -11007,154 +10907,154 @@
     </row>
     <row r="28" spans="1:15" ht="23" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
+      <c r="B28" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
+      <c r="B29" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
+      <c r="B30" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
+      <c r="B31" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19"/>
+      <c r="B32" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
+      <c r="B33" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19"/>
+      <c r="B34" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19"/>
+      <c r="B35" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23" customHeight="1">
@@ -11302,7 +11202,7 @@
     <row r="1" spans="1:22" ht="22" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="28" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C1" s="28"/>
       <c r="D1" s="28"/>
@@ -11376,67 +11276,67 @@
     <row r="4" spans="1:22" ht="35" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="12" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="M4" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4" s="12" t="s">
-        <v>29</v>
-      </c>
       <c r="O4" s="12" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="P4" s="13" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="S4" s="13" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="T4" s="13" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="U4" s="13" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="V4" s="13" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1">
@@ -11475,7 +11375,7 @@
       </c>
       <c r="J5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R5)+(INDEX(Parameters!$J$13:$N$13,1,R5+1)-INDEX(Parameters!$J$13:$N$13,1,R5))*U5,INDEX(Parameters!$D$13:$H$13,1,R5)+(INDEX(Parameters!$D$13:$H$13,1,R5+1)-INDEX(Parameters!$D$13:$H$13,1,R5))*U5)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R5)+(INDEX(Parameters!$D$14:$H$14,1,R5+1)-INDEX(Parameters!$D$14:$H$14,1,R5))*U5)</f>
@@ -11483,11 +11383,11 @@
       </c>
       <c r="L5" s="7">
         <f>I5+J5</f>
-        <v>1508</v>
+        <v>2008</v>
       </c>
       <c r="M5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="N5" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S5)+(INDEX(Parameters!$J$18:$N$18,1,S5+1)-INDEX(Parameters!$J$18:$N$18,1,S5))*V5,INDEX(Parameters!$D$18:$H$18,1,S5)+(INDEX(Parameters!$D$18:$H$18,1,S5+1)-INDEX(Parameters!$D$18:$H$18,1,S5))*V5)</f>
@@ -11499,7 +11399,7 @@
       </c>
       <c r="P5" s="8">
         <f>M5*O5</f>
-        <v>990</v>
+        <v>1056</v>
       </c>
       <c r="Q5" s="8">
         <f>MIN(4,MAX(1,INT((1+C5/Parameters!$D$23)*4)+1))</f>
@@ -11562,7 +11462,7 @@
       </c>
       <c r="J6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R6)+(INDEX(Parameters!$J$13:$N$13,1,R6+1)-INDEX(Parameters!$J$13:$N$13,1,R6))*U6,INDEX(Parameters!$D$13:$H$13,1,R6)+(INDEX(Parameters!$D$13:$H$13,1,R6+1)-INDEX(Parameters!$D$13:$H$13,1,R6))*U6)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R6)+(INDEX(Parameters!$D$14:$H$14,1,R6+1)-INDEX(Parameters!$D$14:$H$14,1,R6))*U6)</f>
@@ -11570,11 +11470,11 @@
       </c>
       <c r="L6" s="7">
         <f>I6+J6</f>
-        <v>1796</v>
+        <v>2296</v>
       </c>
       <c r="M6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
-        <v>2000</v>
+        <v>2050</v>
       </c>
       <c r="N6" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S6)+(INDEX(Parameters!$J$18:$N$18,1,S6+1)-INDEX(Parameters!$J$18:$N$18,1,S6))*V6,INDEX(Parameters!$D$18:$H$18,1,S6)+(INDEX(Parameters!$D$18:$H$18,1,S6+1)-INDEX(Parameters!$D$18:$H$18,1,S6))*V6)</f>
@@ -11586,7 +11486,7 @@
       </c>
       <c r="P6" s="8">
         <f>M6*O6</f>
-        <v>1240</v>
+        <v>1271</v>
       </c>
       <c r="Q6" s="8">
         <f>MIN(4,MAX(1,INT((1+C6/Parameters!$D$23)*4)+1))</f>
@@ -11649,7 +11549,7 @@
       </c>
       <c r="J7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R7)+(INDEX(Parameters!$J$13:$N$13,1,R7+1)-INDEX(Parameters!$J$13:$N$13,1,R7))*U7,INDEX(Parameters!$D$13:$H$13,1,R7)+(INDEX(Parameters!$D$13:$H$13,1,R7+1)-INDEX(Parameters!$D$13:$H$13,1,R7))*U7)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R7)+(INDEX(Parameters!$D$14:$H$14,1,R7+1)-INDEX(Parameters!$D$14:$H$14,1,R7))*U7)</f>
@@ -11657,7 +11557,7 @@
       </c>
       <c r="L7" s="7">
         <f>I7+J7</f>
-        <v>2060</v>
+        <v>2560</v>
       </c>
       <c r="M7" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
@@ -11736,7 +11636,7 @@
       </c>
       <c r="J8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R8)+(INDEX(Parameters!$J$13:$N$13,1,R8+1)-INDEX(Parameters!$J$13:$N$13,1,R8))*U8,INDEX(Parameters!$D$13:$H$13,1,R8)+(INDEX(Parameters!$D$13:$H$13,1,R8+1)-INDEX(Parameters!$D$13:$H$13,1,R8))*U8)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R8)+(INDEX(Parameters!$D$14:$H$14,1,R8+1)-INDEX(Parameters!$D$14:$H$14,1,R8))*U8)</f>
@@ -11744,11 +11644,11 @@
       </c>
       <c r="L8" s="7">
         <f>I8+J8</f>
-        <v>2300</v>
+        <v>2800</v>
       </c>
       <c r="M8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
-        <v>3000</v>
+        <v>2950</v>
       </c>
       <c r="N8" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S8)+(INDEX(Parameters!$J$18:$N$18,1,S8+1)-INDEX(Parameters!$J$18:$N$18,1,S8))*V8,INDEX(Parameters!$D$18:$H$18,1,S8)+(INDEX(Parameters!$D$18:$H$18,1,S8+1)-INDEX(Parameters!$D$18:$H$18,1,S8))*V8)</f>
@@ -11760,7 +11660,7 @@
       </c>
       <c r="P8" s="8">
         <f>M8*O8</f>
-        <v>1620</v>
+        <v>1593</v>
       </c>
       <c r="Q8" s="8">
         <f>MIN(4,MAX(1,INT((1+C8/Parameters!$D$23)*4)+1))</f>
@@ -11823,7 +11723,7 @@
       </c>
       <c r="J9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R9)+(INDEX(Parameters!$J$13:$N$13,1,R9+1)-INDEX(Parameters!$J$13:$N$13,1,R9))*U9,INDEX(Parameters!$D$13:$H$13,1,R9)+(INDEX(Parameters!$D$13:$H$13,1,R9+1)-INDEX(Parameters!$D$13:$H$13,1,R9))*U9)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R9)+(INDEX(Parameters!$D$14:$H$14,1,R9+1)-INDEX(Parameters!$D$14:$H$14,1,R9))*U9)</f>
@@ -11831,11 +11731,11 @@
       </c>
       <c r="L9" s="7">
         <f>I9+J9</f>
-        <v>2516</v>
+        <v>3016</v>
       </c>
       <c r="M9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="N9" s="7">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S9)+(INDEX(Parameters!$J$18:$N$18,1,S9+1)-INDEX(Parameters!$J$18:$N$18,1,S9))*V9,INDEX(Parameters!$D$18:$H$18,1,S9)+(INDEX(Parameters!$D$18:$H$18,1,S9+1)-INDEX(Parameters!$D$18:$H$18,1,S9))*V9)</f>
@@ -11847,7 +11747,7 @@
       </c>
       <c r="P9" s="8">
         <f>M9*O9</f>
-        <v>1750</v>
+        <v>1700</v>
       </c>
       <c r="Q9" s="8">
         <f>MIN(4,MAX(1,INT((1+C9/Parameters!$D$23)*4)+1))</f>
@@ -11949,7 +11849,7 @@
     <row r="13" spans="1:22" ht="22" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="10" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C13" s="10" t="str">
         <f>B5</f>
@@ -12527,23 +12427,23 @@
       </c>
       <c r="C27" s="14">
         <f t="shared" si="0"/>
-        <v>957.40000000000009</v>
+        <v>982.40000000000009</v>
       </c>
       <c r="D27" s="14">
         <f t="shared" si="1"/>
-        <v>1253.8000000000002</v>
+        <v>1278.8000000000002</v>
       </c>
       <c r="E27" s="14">
         <f t="shared" si="2"/>
-        <v>1543</v>
+        <v>1568</v>
       </c>
       <c r="F27" s="14">
         <f t="shared" si="3"/>
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="G27" s="14">
         <f t="shared" si="4"/>
-        <v>2099.8000000000002</v>
+        <v>2124.8000000000002</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -12568,23 +12468,23 @@
       </c>
       <c r="C28" s="14">
         <f t="shared" si="0"/>
-        <v>1032.8</v>
+        <v>1082.8</v>
       </c>
       <c r="D28" s="14">
         <f t="shared" si="1"/>
-        <v>1343.6</v>
+        <v>1393.6</v>
       </c>
       <c r="E28" s="14">
         <f t="shared" si="2"/>
-        <v>1646</v>
+        <v>1696</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" si="3"/>
-        <v>1940</v>
+        <v>1990</v>
       </c>
       <c r="G28" s="14">
         <f t="shared" si="4"/>
-        <v>2225.6</v>
+        <v>2275.6</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -12609,23 +12509,23 @@
       </c>
       <c r="C29" s="14">
         <f t="shared" si="0"/>
-        <v>1108.2</v>
+        <v>1183.2</v>
       </c>
       <c r="D29" s="14">
         <f t="shared" si="1"/>
-        <v>1433.4</v>
+        <v>1508.4</v>
       </c>
       <c r="E29" s="14">
         <f t="shared" si="2"/>
-        <v>1749</v>
+        <v>1824</v>
       </c>
       <c r="F29" s="14">
         <f t="shared" si="3"/>
-        <v>2055</v>
+        <v>2130</v>
       </c>
       <c r="G29" s="14">
         <f t="shared" si="4"/>
-        <v>2351.4</v>
+        <v>2426.4</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -12650,23 +12550,23 @@
       </c>
       <c r="C30" s="14">
         <f t="shared" si="0"/>
-        <v>1183.6000000000001</v>
+        <v>1283.6000000000001</v>
       </c>
       <c r="D30" s="14">
         <f t="shared" si="1"/>
-        <v>1523.2</v>
+        <v>1623.2</v>
       </c>
       <c r="E30" s="14">
         <f t="shared" si="2"/>
-        <v>1852</v>
+        <v>1952</v>
       </c>
       <c r="F30" s="14">
         <f t="shared" si="3"/>
-        <v>2170</v>
+        <v>2270</v>
       </c>
       <c r="G30" s="14">
         <f t="shared" si="4"/>
-        <v>2477.2000000000003</v>
+        <v>2577.2000000000003</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -12691,23 +12591,23 @@
       </c>
       <c r="C31" s="14">
         <f t="shared" si="0"/>
-        <v>1259</v>
+        <v>1384</v>
       </c>
       <c r="D31" s="14">
         <f t="shared" si="1"/>
-        <v>1613</v>
+        <v>1738</v>
       </c>
       <c r="E31" s="14">
         <f t="shared" si="2"/>
-        <v>1955</v>
+        <v>2080</v>
       </c>
       <c r="F31" s="14">
         <f t="shared" si="3"/>
-        <v>2285</v>
+        <v>2410</v>
       </c>
       <c r="G31" s="14">
         <f t="shared" si="4"/>
-        <v>2603</v>
+        <v>2728</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -12732,23 +12632,23 @@
       </c>
       <c r="C32" s="14">
         <f t="shared" si="0"/>
-        <v>1334.4</v>
+        <v>1484.4</v>
       </c>
       <c r="D32" s="14">
         <f t="shared" si="1"/>
-        <v>1702.8000000000002</v>
+        <v>1852.8000000000002</v>
       </c>
       <c r="E32" s="14">
         <f t="shared" si="2"/>
-        <v>2058</v>
+        <v>2208</v>
       </c>
       <c r="F32" s="14">
         <f t="shared" si="3"/>
-        <v>2400</v>
+        <v>2550</v>
       </c>
       <c r="G32" s="14">
         <f t="shared" si="4"/>
-        <v>2728.8</v>
+        <v>2878.8</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -12773,23 +12673,23 @@
       </c>
       <c r="C33" s="14">
         <f t="shared" si="0"/>
-        <v>1409.8000000000002</v>
+        <v>1584.8000000000002</v>
       </c>
       <c r="D33" s="14">
         <f t="shared" si="1"/>
-        <v>1792.6</v>
+        <v>1967.6</v>
       </c>
       <c r="E33" s="14">
         <f t="shared" si="2"/>
-        <v>2161</v>
+        <v>2336</v>
       </c>
       <c r="F33" s="14">
         <f t="shared" si="3"/>
-        <v>2515</v>
+        <v>2690</v>
       </c>
       <c r="G33" s="14">
         <f t="shared" si="4"/>
-        <v>2854.6</v>
+        <v>3029.6</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
@@ -12814,23 +12714,23 @@
       </c>
       <c r="C34" s="14">
         <f t="shared" si="0"/>
-        <v>1485.2</v>
+        <v>1685.2</v>
       </c>
       <c r="D34" s="14">
         <f t="shared" si="1"/>
-        <v>1882.4</v>
+        <v>2082.4</v>
       </c>
       <c r="E34" s="14">
         <f t="shared" si="2"/>
-        <v>2264</v>
+        <v>2464</v>
       </c>
       <c r="F34" s="14">
         <f t="shared" si="3"/>
-        <v>2630</v>
+        <v>2830</v>
       </c>
       <c r="G34" s="14">
         <f t="shared" si="4"/>
-        <v>2980.4</v>
+        <v>3180.4</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -12995,7 +12895,7 @@
     <row r="41" spans="1:22" ht="22" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="28" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="C41" s="28"/>
       <c r="D41" s="28"/>
@@ -13067,67 +12967,67 @@
     </row>
     <row r="44" spans="1:22" ht="35" customHeight="1">
       <c r="B44" s="13" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F44" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K44" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="L44" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M44" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="N44" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G44" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H44" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="I44" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="J44" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="K44" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="L44" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="M44" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="N44" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="O44" s="13" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="P44" s="13" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="Q44" s="13" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="R44" s="13" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="S44" s="13" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="T44" s="13" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="U44" s="13" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="V44" s="13" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:22" ht="22" customHeight="1">
@@ -13149,47 +13049,47 @@
       </c>
       <c r="F45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q45)+(INDEX(Parameters!$J$10:$N$10,1,Q45+1)-INDEX(Parameters!$J$10:$N$10,1,Q45))*T45,INDEX(Parameters!$D$10:$H$10,1,Q45)+(INDEX(Parameters!$D$10:$H$10,1,Q45+1)-INDEX(Parameters!$D$10:$H$10,1,Q45))*T45)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R45)+(INDEX(Parameters!$J$11:$N$11,1,R45+1)-INDEX(Parameters!$J$11:$N$11,1,R45))*U45,INDEX(Parameters!$D$11:$H$11,1,Q45)+(INDEX(Parameters!$D$11:$H$11,1,Q45+1)-INDEX(Parameters!$D$11:$H$11,1,Q45))*T45)</f>
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="H45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q45)+(INDEX(Parameters!$J$12:$N$12,1,Q45+1)-INDEX(Parameters!$J$12:$N$12,1,Q45))*T45,INDEX(Parameters!$D$12:$H$12,1,Q45)+(INDEX(Parameters!$D$12:$H$12,1,Q45+1)-INDEX(Parameters!$D$12:$H$12,1,Q45))*T45)</f>
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="I45" s="8">
         <f>F45*H45</f>
-        <v>2250</v>
+        <v>1560</v>
       </c>
       <c r="J45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R45)+(INDEX(Parameters!$D$14:$H$14,1,R45+1)-INDEX(Parameters!$D$14:$H$14,1,R45))*U45)</f>
-        <v>0.57999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="L45" s="8">
         <f>I45+J45</f>
-        <v>2750</v>
+        <v>2560</v>
       </c>
       <c r="M45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="N45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S45)+(INDEX(Parameters!$J$18:$N$18,1,S45+1)-INDEX(Parameters!$J$18:$N$18,1,S45))*V45,INDEX(Parameters!$D$18:$H$18,1,S45)+(INDEX(Parameters!$D$18:$H$18,1,S45+1)-INDEX(Parameters!$D$18:$H$18,1,S45))*V45)</f>
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="O45" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S45)+(INDEX(Parameters!$J$19:$N$19,1,S45+1)-INDEX(Parameters!$J$19:$N$19,1,S45))*V45,INDEX(Parameters!$D$19:$H$19,1,S45)+(INDEX(Parameters!$D$19:$H$19,1,S45+1)-INDEX(Parameters!$D$19:$H$19,1,S45))*V45)</f>
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="P45" s="8">
         <f>M45*O45</f>
-        <v>880</v>
+        <v>1056</v>
       </c>
       <c r="Q45" s="8">
         <f>MIN(4,MAX(1,INT((1+C45/Parameters!$D$23)*4)+1))</f>
@@ -13235,47 +13135,47 @@
       </c>
       <c r="F46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q46)+(INDEX(Parameters!$J$10:$N$10,1,Q46+1)-INDEX(Parameters!$J$10:$N$10,1,Q46))*T46,INDEX(Parameters!$D$10:$H$10,1,Q46)+(INDEX(Parameters!$D$10:$H$10,1,Q46+1)-INDEX(Parameters!$D$10:$H$10,1,Q46))*T46)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R46)+(INDEX(Parameters!$J$11:$N$11,1,R46+1)-INDEX(Parameters!$J$11:$N$11,1,R46))*U46,INDEX(Parameters!$D$11:$H$11,1,Q46)+(INDEX(Parameters!$D$11:$H$11,1,Q46+1)-INDEX(Parameters!$D$11:$H$11,1,Q46))*T46)</f>
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="H46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q46)+(INDEX(Parameters!$J$12:$N$12,1,Q46+1)-INDEX(Parameters!$J$12:$N$12,1,Q46))*T46,INDEX(Parameters!$D$12:$H$12,1,Q46)+(INDEX(Parameters!$D$12:$H$12,1,Q46+1)-INDEX(Parameters!$D$12:$H$12,1,Q46))*T46)</f>
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="I46" s="8">
         <f>F46*H46</f>
-        <v>2250</v>
+        <v>1560</v>
       </c>
       <c r="J46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="K46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="L46" s="8">
         <f>I46+J46</f>
-        <v>3500</v>
+        <v>2560</v>
       </c>
       <c r="M46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
-        <v>1500</v>
+        <v>2050</v>
       </c>
       <c r="N46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S46)+(INDEX(Parameters!$J$18:$N$18,1,S46+1)-INDEX(Parameters!$J$18:$N$18,1,S46))*V46,INDEX(Parameters!$D$18:$H$18,1,S46)+(INDEX(Parameters!$D$18:$H$18,1,S46+1)-INDEX(Parameters!$D$18:$H$18,1,S46))*V46)</f>
-        <v>0.255</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="O46" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S46)+(INDEX(Parameters!$J$19:$N$19,1,S46+1)-INDEX(Parameters!$J$19:$N$19,1,S46))*V46,INDEX(Parameters!$D$19:$H$19,1,S46)+(INDEX(Parameters!$D$19:$H$19,1,S46+1)-INDEX(Parameters!$D$19:$H$19,1,S46))*V46)</f>
-        <v>0.84000000000000008</v>
+        <v>0.62</v>
       </c>
       <c r="P46" s="8">
         <f>M46*O46</f>
-        <v>1260.0000000000002</v>
+        <v>1271</v>
       </c>
       <c r="Q46" s="8">
         <f>MIN(4,MAX(1,INT((1+C46/Parameters!$D$23)*4)+1))</f>
@@ -13321,23 +13221,23 @@
       </c>
       <c r="F47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q47)+(INDEX(Parameters!$J$10:$N$10,1,Q47+1)-INDEX(Parameters!$J$10:$N$10,1,Q47))*T47,INDEX(Parameters!$D$10:$H$10,1,Q47)+(INDEX(Parameters!$D$10:$H$10,1,Q47+1)-INDEX(Parameters!$D$10:$H$10,1,Q47))*T47)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R47)+(INDEX(Parameters!$J$11:$N$11,1,R47+1)-INDEX(Parameters!$J$11:$N$11,1,R47))*U47,INDEX(Parameters!$D$11:$H$11,1,Q47)+(INDEX(Parameters!$D$11:$H$11,1,Q47+1)-INDEX(Parameters!$D$11:$H$11,1,Q47))*T47)</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q47)+(INDEX(Parameters!$J$12:$N$12,1,Q47+1)-INDEX(Parameters!$J$12:$N$12,1,Q47))*T47,INDEX(Parameters!$D$12:$H$12,1,Q47)+(INDEX(Parameters!$D$12:$H$12,1,Q47+1)-INDEX(Parameters!$D$12:$H$12,1,Q47))*T47)</f>
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="I47" s="8">
         <f>F47*H47</f>
-        <v>2250</v>
+        <v>1560</v>
       </c>
       <c r="J47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="K47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R47)+(INDEX(Parameters!$D$14:$H$14,1,R47+1)-INDEX(Parameters!$D$14:$H$14,1,R47))*U47)</f>
@@ -13345,23 +13245,23 @@
       </c>
       <c r="L47" s="8">
         <f>I47+J47</f>
-        <v>4250</v>
+        <v>2560</v>
       </c>
       <c r="M47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="N47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S47)+(INDEX(Parameters!$J$18:$N$18,1,S47+1)-INDEX(Parameters!$J$18:$N$18,1,S47))*V47,INDEX(Parameters!$D$18:$H$18,1,S47)+(INDEX(Parameters!$D$18:$H$18,1,S47+1)-INDEX(Parameters!$D$18:$H$18,1,S47))*V47)</f>
-        <v>0.28000000000000003</v>
+        <v>0.25</v>
       </c>
       <c r="O47" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S47)+(INDEX(Parameters!$J$19:$N$19,1,S47+1)-INDEX(Parameters!$J$19:$N$19,1,S47))*V47,INDEX(Parameters!$D$19:$H$19,1,S47)+(INDEX(Parameters!$D$19:$H$19,1,S47+1)-INDEX(Parameters!$D$19:$H$19,1,S47))*V47)</f>
-        <v>0.8</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P47" s="8">
         <f>M47*O47</f>
-        <v>1600</v>
+        <v>1450</v>
       </c>
       <c r="Q47" s="8">
         <f>MIN(4,MAX(1,INT((1+C47/Parameters!$D$23)*4)+1))</f>
@@ -13407,47 +13307,47 @@
       </c>
       <c r="F48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q48)+(INDEX(Parameters!$J$10:$N$10,1,Q48+1)-INDEX(Parameters!$J$10:$N$10,1,Q48))*T48,INDEX(Parameters!$D$10:$H$10,1,Q48)+(INDEX(Parameters!$D$10:$H$10,1,Q48+1)-INDEX(Parameters!$D$10:$H$10,1,Q48))*T48)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R48)+(INDEX(Parameters!$J$11:$N$11,1,R48+1)-INDEX(Parameters!$J$11:$N$11,1,R48))*U48,INDEX(Parameters!$D$11:$H$11,1,Q48)+(INDEX(Parameters!$D$11:$H$11,1,Q48+1)-INDEX(Parameters!$D$11:$H$11,1,Q48))*T48)</f>
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="H48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q48)+(INDEX(Parameters!$J$12:$N$12,1,Q48+1)-INDEX(Parameters!$J$12:$N$12,1,Q48))*T48,INDEX(Parameters!$D$12:$H$12,1,Q48)+(INDEX(Parameters!$D$12:$H$12,1,Q48+1)-INDEX(Parameters!$D$12:$H$12,1,Q48))*T48)</f>
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="I48" s="8">
         <f>F48*H48</f>
-        <v>2250</v>
+        <v>1560</v>
       </c>
       <c r="J48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>2750</v>
+        <v>1000</v>
       </c>
       <c r="K48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="L48" s="8">
         <f>I48+J48</f>
-        <v>5000</v>
+        <v>2560</v>
       </c>
       <c r="M48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
-        <v>2500</v>
+        <v>2950</v>
       </c>
       <c r="N48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S48)+(INDEX(Parameters!$J$18:$N$18,1,S48+1)-INDEX(Parameters!$J$18:$N$18,1,S48))*V48,INDEX(Parameters!$D$18:$H$18,1,S48)+(INDEX(Parameters!$D$18:$H$18,1,S48+1)-INDEX(Parameters!$D$18:$H$18,1,S48))*V48)</f>
-        <v>0.30500000000000005</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="O48" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S48)+(INDEX(Parameters!$J$19:$N$19,1,S48+1)-INDEX(Parameters!$J$19:$N$19,1,S48))*V48,INDEX(Parameters!$D$19:$H$19,1,S48)+(INDEX(Parameters!$D$19:$H$19,1,S48+1)-INDEX(Parameters!$D$19:$H$19,1,S48))*V48)</f>
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="P48" s="8">
         <f>M48*O48</f>
-        <v>1900</v>
+        <v>1593</v>
       </c>
       <c r="Q48" s="8">
         <f>MIN(4,MAX(1,INT((1+C48/Parameters!$D$23)*4)+1))</f>
@@ -13493,47 +13393,47 @@
       </c>
       <c r="F49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q49)+(INDEX(Parameters!$J$10:$N$10,1,Q49+1)-INDEX(Parameters!$J$10:$N$10,1,Q49))*T49,INDEX(Parameters!$D$10:$H$10,1,Q49)+(INDEX(Parameters!$D$10:$H$10,1,Q49+1)-INDEX(Parameters!$D$10:$H$10,1,Q49))*T49)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R49)+(INDEX(Parameters!$J$11:$N$11,1,R49+1)-INDEX(Parameters!$J$11:$N$11,1,R49))*U49,INDEX(Parameters!$D$11:$H$11,1,Q49)+(INDEX(Parameters!$D$11:$H$11,1,Q49+1)-INDEX(Parameters!$D$11:$H$11,1,Q49))*T49)</f>
-        <v>0.12</v>
+        <v>0.45</v>
       </c>
       <c r="H49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q49)+(INDEX(Parameters!$J$12:$N$12,1,Q49+1)-INDEX(Parameters!$J$12:$N$12,1,Q49))*T49,INDEX(Parameters!$D$12:$H$12,1,Q49)+(INDEX(Parameters!$D$12:$H$12,1,Q49+1)-INDEX(Parameters!$D$12:$H$12,1,Q49))*T49)</f>
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="I49" s="8">
         <f>F49*H49</f>
-        <v>2250</v>
+        <v>1560</v>
       </c>
       <c r="J49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="K49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L49" s="8">
         <f>I49+J49</f>
-        <v>5750</v>
+        <v>2560</v>
       </c>
       <c r="M49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
-        <v>3000</v>
+        <v>3400</v>
       </c>
       <c r="N49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S49)+(INDEX(Parameters!$J$18:$N$18,1,S49+1)-INDEX(Parameters!$J$18:$N$18,1,S49))*V49,INDEX(Parameters!$D$18:$H$18,1,S49)+(INDEX(Parameters!$D$18:$H$18,1,S49+1)-INDEX(Parameters!$D$18:$H$18,1,S49))*V49)</f>
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O49" s="8">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S49)+(INDEX(Parameters!$J$19:$N$19,1,S49+1)-INDEX(Parameters!$J$19:$N$19,1,S49))*V49,INDEX(Parameters!$D$19:$H$19,1,S49)+(INDEX(Parameters!$D$19:$H$19,1,S49+1)-INDEX(Parameters!$D$19:$H$19,1,S49))*V49)</f>
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="P49" s="8">
         <f>M49*O49</f>
-        <v>2160</v>
+        <v>1700</v>
       </c>
       <c r="Q49" s="8">
         <f>MIN(4,MAX(1,INT((1+C49/Parameters!$D$23)*4)+1))</f>
@@ -13631,7 +13531,7 @@
     </row>
     <row r="53" spans="2:22" ht="22" customHeight="1">
       <c r="B53" s="11" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C53" s="11" t="str">
         <f>B45</f>
@@ -13715,23 +13615,23 @@
       </c>
       <c r="C55" s="15">
         <f t="shared" si="5"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="D55" s="15">
         <f t="shared" si="6"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E55" s="15">
         <f t="shared" si="7"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F55" s="15">
         <f t="shared" si="8"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="G55" s="15">
         <f t="shared" si="9"/>
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
@@ -13755,23 +13655,23 @@
       </c>
       <c r="C56" s="15">
         <f t="shared" si="5"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D56" s="15">
         <f t="shared" si="6"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E56" s="15">
         <f t="shared" si="7"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="F56" s="15">
         <f t="shared" si="8"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G56" s="15">
         <f t="shared" si="9"/>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
@@ -13795,23 +13695,23 @@
       </c>
       <c r="C57" s="15">
         <f t="shared" si="5"/>
-        <v>367.5</v>
+        <v>450</v>
       </c>
       <c r="D57" s="15">
         <f t="shared" si="6"/>
-        <v>367.5</v>
+        <v>450</v>
       </c>
       <c r="E57" s="15">
         <f t="shared" si="7"/>
-        <v>367.5</v>
+        <v>450</v>
       </c>
       <c r="F57" s="15">
         <f t="shared" si="8"/>
-        <v>367.5</v>
+        <v>450</v>
       </c>
       <c r="G57" s="15">
         <f t="shared" si="9"/>
-        <v>367.5</v>
+        <v>450</v>
       </c>
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
@@ -13835,23 +13735,23 @@
       </c>
       <c r="C58" s="15">
         <f t="shared" si="5"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="D58" s="15">
         <f t="shared" si="6"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="E58" s="15">
         <f t="shared" si="7"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="F58" s="15">
         <f t="shared" si="8"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="G58" s="15">
         <f t="shared" si="9"/>
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
@@ -13875,23 +13775,23 @@
       </c>
       <c r="C59" s="15">
         <f t="shared" si="5"/>
-        <v>592.5</v>
+        <v>750</v>
       </c>
       <c r="D59" s="15">
         <f t="shared" si="6"/>
-        <v>592.5</v>
+        <v>750</v>
       </c>
       <c r="E59" s="15">
         <f t="shared" si="7"/>
-        <v>592.5</v>
+        <v>750</v>
       </c>
       <c r="F59" s="15">
         <f t="shared" si="8"/>
-        <v>592.5</v>
+        <v>750</v>
       </c>
       <c r="G59" s="15">
         <f t="shared" si="9"/>
-        <v>592.5</v>
+        <v>750</v>
       </c>
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
@@ -13915,23 +13815,23 @@
       </c>
       <c r="C60" s="15">
         <f t="shared" si="5"/>
-        <v>705</v>
+        <v>828</v>
       </c>
       <c r="D60" s="15">
         <f t="shared" si="6"/>
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="E60" s="15">
         <f t="shared" si="7"/>
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="F60" s="15">
         <f t="shared" si="8"/>
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="G60" s="15">
         <f t="shared" si="9"/>
-        <v>705</v>
+        <v>900</v>
       </c>
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
@@ -13955,23 +13855,23 @@
       </c>
       <c r="C61" s="15">
         <f t="shared" si="5"/>
-        <v>817.5</v>
+        <v>906</v>
       </c>
       <c r="D61" s="15">
         <f t="shared" si="6"/>
-        <v>817.5</v>
+        <v>978</v>
       </c>
       <c r="E61" s="15">
         <f t="shared" si="7"/>
-        <v>817.5</v>
+        <v>1050</v>
       </c>
       <c r="F61" s="15">
         <f t="shared" si="8"/>
-        <v>817.5</v>
+        <v>1050</v>
       </c>
       <c r="G61" s="15">
         <f t="shared" si="9"/>
-        <v>817.5</v>
+        <v>1050</v>
       </c>
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
@@ -13995,23 +13895,23 @@
       </c>
       <c r="C62" s="15">
         <f t="shared" si="5"/>
-        <v>930.00000000000011</v>
+        <v>984</v>
       </c>
       <c r="D62" s="15">
         <f t="shared" si="6"/>
-        <v>930.00000000000011</v>
+        <v>1056</v>
       </c>
       <c r="E62" s="15">
         <f t="shared" si="7"/>
-        <v>930.00000000000011</v>
+        <v>1128</v>
       </c>
       <c r="F62" s="15">
         <f t="shared" si="8"/>
-        <v>930.00000000000011</v>
+        <v>1200</v>
       </c>
       <c r="G62" s="15">
         <f t="shared" si="9"/>
-        <v>930.00000000000011</v>
+        <v>1200</v>
       </c>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
@@ -14035,23 +13935,23 @@
       </c>
       <c r="C63" s="15">
         <f t="shared" si="5"/>
-        <v>1042.5</v>
+        <v>1062</v>
       </c>
       <c r="D63" s="15">
         <f t="shared" si="6"/>
-        <v>1042.5</v>
+        <v>1134</v>
       </c>
       <c r="E63" s="15">
         <f t="shared" si="7"/>
-        <v>1042.5</v>
+        <v>1206</v>
       </c>
       <c r="F63" s="15">
         <f t="shared" si="8"/>
-        <v>1042.5</v>
+        <v>1278</v>
       </c>
       <c r="G63" s="15">
         <f t="shared" si="9"/>
-        <v>1042.5</v>
+        <v>1350</v>
       </c>
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
@@ -14075,23 +13975,23 @@
       </c>
       <c r="C64" s="15">
         <f t="shared" si="5"/>
-        <v>1155</v>
+        <v>1140</v>
       </c>
       <c r="D64" s="15">
         <f t="shared" si="6"/>
-        <v>1155</v>
+        <v>1212</v>
       </c>
       <c r="E64" s="15">
         <f t="shared" si="7"/>
-        <v>1155</v>
+        <v>1284</v>
       </c>
       <c r="F64" s="15">
         <f t="shared" si="8"/>
-        <v>1155</v>
+        <v>1356</v>
       </c>
       <c r="G64" s="15">
         <f t="shared" si="9"/>
-        <v>1155</v>
+        <v>1428</v>
       </c>
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
@@ -14115,23 +14015,23 @@
       </c>
       <c r="C65" s="15">
         <f t="shared" si="5"/>
-        <v>1267.5</v>
+        <v>1218</v>
       </c>
       <c r="D65" s="15">
         <f t="shared" si="6"/>
-        <v>1267.5</v>
+        <v>1290</v>
       </c>
       <c r="E65" s="15">
         <f t="shared" si="7"/>
-        <v>1267.5</v>
+        <v>1362</v>
       </c>
       <c r="F65" s="15">
         <f t="shared" si="8"/>
-        <v>1267.5</v>
+        <v>1434</v>
       </c>
       <c r="G65" s="15">
         <f t="shared" si="9"/>
-        <v>1267.5</v>
+        <v>1506</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
@@ -14155,23 +14055,23 @@
       </c>
       <c r="C66" s="15">
         <f t="shared" si="5"/>
-        <v>1390</v>
+        <v>1296</v>
       </c>
       <c r="D66" s="15">
         <f t="shared" si="6"/>
-        <v>1392.5</v>
+        <v>1368</v>
       </c>
       <c r="E66" s="15">
         <f t="shared" si="7"/>
-        <v>1380</v>
+        <v>1440</v>
       </c>
       <c r="F66" s="15">
         <f t="shared" si="8"/>
-        <v>1380</v>
+        <v>1512</v>
       </c>
       <c r="G66" s="15">
         <f t="shared" si="9"/>
-        <v>1380</v>
+        <v>1584</v>
       </c>
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
@@ -14195,23 +14095,23 @@
       </c>
       <c r="C67" s="15">
         <f t="shared" si="5"/>
-        <v>1527.5</v>
+        <v>1424</v>
       </c>
       <c r="D67" s="15">
         <f t="shared" si="6"/>
-        <v>1567.5</v>
+        <v>1496</v>
       </c>
       <c r="E67" s="15">
         <f t="shared" si="7"/>
-        <v>1592.5</v>
+        <v>1568</v>
       </c>
       <c r="F67" s="15">
         <f t="shared" si="8"/>
-        <v>1602.5</v>
+        <v>1640</v>
       </c>
       <c r="G67" s="15">
         <f t="shared" si="9"/>
-        <v>1597.5</v>
+        <v>1712</v>
       </c>
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
@@ -14235,23 +14135,23 @@
       </c>
       <c r="C68" s="15">
         <f t="shared" si="5"/>
-        <v>1665</v>
+        <v>1552</v>
       </c>
       <c r="D68" s="15">
         <f t="shared" si="6"/>
-        <v>1742.5</v>
+        <v>1624</v>
       </c>
       <c r="E68" s="15">
         <f t="shared" si="7"/>
-        <v>1805</v>
+        <v>1696</v>
       </c>
       <c r="F68" s="15">
         <f t="shared" si="8"/>
-        <v>1852.5</v>
+        <v>1768</v>
       </c>
       <c r="G68" s="15">
         <f t="shared" si="9"/>
-        <v>1885</v>
+        <v>1840</v>
       </c>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
@@ -14275,23 +14175,23 @@
       </c>
       <c r="C69" s="15">
         <f t="shared" si="5"/>
-        <v>1802.5</v>
+        <v>1680</v>
       </c>
       <c r="D69" s="15">
         <f t="shared" si="6"/>
-        <v>1917.5</v>
+        <v>1752</v>
       </c>
       <c r="E69" s="15">
         <f t="shared" si="7"/>
-        <v>2017.5</v>
+        <v>1824</v>
       </c>
       <c r="F69" s="15">
         <f t="shared" si="8"/>
-        <v>2102.5</v>
+        <v>1896</v>
       </c>
       <c r="G69" s="15">
         <f t="shared" si="9"/>
-        <v>2172.5</v>
+        <v>1968</v>
       </c>
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
@@ -14315,23 +14215,23 @@
       </c>
       <c r="C70" s="15">
         <f t="shared" si="5"/>
-        <v>1940</v>
+        <v>1808</v>
       </c>
       <c r="D70" s="15">
         <f t="shared" si="6"/>
-        <v>2092.5</v>
+        <v>1880</v>
       </c>
       <c r="E70" s="15">
         <f t="shared" si="7"/>
-        <v>2230</v>
+        <v>1952</v>
       </c>
       <c r="F70" s="15">
         <f t="shared" si="8"/>
-        <v>2352.5</v>
+        <v>2024</v>
       </c>
       <c r="G70" s="15">
         <f t="shared" si="9"/>
-        <v>2460</v>
+        <v>2096</v>
       </c>
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
@@ -14355,23 +14255,23 @@
       </c>
       <c r="C71" s="15">
         <f t="shared" si="5"/>
-        <v>2077.5</v>
+        <v>1936</v>
       </c>
       <c r="D71" s="15">
         <f t="shared" si="6"/>
-        <v>2267.5</v>
+        <v>2008</v>
       </c>
       <c r="E71" s="15">
         <f t="shared" si="7"/>
-        <v>2442.5</v>
+        <v>2080</v>
       </c>
       <c r="F71" s="15">
         <f t="shared" si="8"/>
-        <v>2602.5</v>
+        <v>2152</v>
       </c>
       <c r="G71" s="15">
         <f t="shared" si="9"/>
-        <v>2747.5</v>
+        <v>2224</v>
       </c>
       <c r="H71" s="8"/>
       <c r="I71" s="8"/>
@@ -14395,23 +14295,23 @@
       </c>
       <c r="C72" s="15">
         <f t="shared" si="5"/>
-        <v>2215</v>
+        <v>2064</v>
       </c>
       <c r="D72" s="15">
         <f t="shared" si="6"/>
-        <v>2442.5</v>
+        <v>2136</v>
       </c>
       <c r="E72" s="15">
         <f t="shared" si="7"/>
-        <v>2655</v>
+        <v>2208</v>
       </c>
       <c r="F72" s="15">
         <f t="shared" si="8"/>
-        <v>2852.5</v>
+        <v>2280</v>
       </c>
       <c r="G72" s="15">
         <f t="shared" si="9"/>
-        <v>3035</v>
+        <v>2352</v>
       </c>
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
@@ -14435,23 +14335,23 @@
       </c>
       <c r="C73" s="15">
         <f t="shared" si="5"/>
-        <v>2352.5</v>
+        <v>2192</v>
       </c>
       <c r="D73" s="15">
         <f t="shared" si="6"/>
-        <v>2617.5</v>
+        <v>2264</v>
       </c>
       <c r="E73" s="15">
         <f t="shared" si="7"/>
-        <v>2867.5</v>
+        <v>2336</v>
       </c>
       <c r="F73" s="15">
         <f t="shared" si="8"/>
-        <v>3102.5</v>
+        <v>2408</v>
       </c>
       <c r="G73" s="15">
         <f t="shared" si="9"/>
-        <v>3322.5</v>
+        <v>2480</v>
       </c>
       <c r="H73" s="8"/>
       <c r="I73" s="8"/>
@@ -14475,23 +14375,23 @@
       </c>
       <c r="C74" s="15">
         <f t="shared" si="5"/>
-        <v>2490</v>
+        <v>2320</v>
       </c>
       <c r="D74" s="15">
         <f t="shared" si="6"/>
-        <v>2792.5</v>
+        <v>2392</v>
       </c>
       <c r="E74" s="15">
         <f t="shared" si="7"/>
-        <v>3080</v>
+        <v>2464</v>
       </c>
       <c r="F74" s="15">
         <f t="shared" si="8"/>
-        <v>3352.5</v>
+        <v>2536</v>
       </c>
       <c r="G74" s="15">
         <f t="shared" si="9"/>
-        <v>3610</v>
+        <v>2608</v>
       </c>
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
@@ -14649,7 +14549,7 @@
     </row>
     <row r="81" spans="2:22" ht="22" customHeight="1">
       <c r="B81" s="29" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="C81" s="29"/>
       <c r="D81" s="29"/>
@@ -14720,67 +14620,67 @@
     </row>
     <row r="84" spans="2:22" ht="35" customHeight="1">
       <c r="B84" s="13" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D84" s="13" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F84" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H84" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I84" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J84" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K84" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="L84" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M84" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="N84" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G84" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="I84" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="J84" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="K84" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="L84" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="M84" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="N84" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="O84" s="13" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="P84" s="13" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="Q84" s="13" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="R84" s="13" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="S84" s="13" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="T84" s="13" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="U84" s="13" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="V84" s="13" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85" spans="2:22" ht="22" customHeight="1">
@@ -14802,47 +14702,47 @@
       </c>
       <c r="F85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q85)+(INDEX(Parameters!$J$10:$N$10,1,Q85+1)-INDEX(Parameters!$J$10:$N$10,1,Q85))*T85,INDEX(Parameters!$D$10:$H$10,1,Q85)+(INDEX(Parameters!$D$10:$H$10,1,Q85+1)-INDEX(Parameters!$D$10:$H$10,1,Q85))*T85)</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="G85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R85)+(INDEX(Parameters!$J$11:$N$11,1,R85+1)-INDEX(Parameters!$J$11:$N$11,1,R85))*U85,INDEX(Parameters!$D$11:$H$11,1,Q85)+(INDEX(Parameters!$D$11:$H$11,1,Q85+1)-INDEX(Parameters!$D$11:$H$11,1,Q85))*T85)</f>
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="H85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q85)+(INDEX(Parameters!$J$12:$N$12,1,Q85+1)-INDEX(Parameters!$J$12:$N$12,1,Q85))*T85,INDEX(Parameters!$D$12:$H$12,1,Q85)+(INDEX(Parameters!$D$12:$H$12,1,Q85+1)-INDEX(Parameters!$D$12:$H$12,1,Q85))*T85)</f>
-        <v>0.96</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I85" s="8">
         <f>F85*H85</f>
-        <v>960</v>
+        <v>1008.0000000000001</v>
       </c>
       <c r="J85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R85)+(INDEX(Parameters!$J$13:$N$13,1,R85+1)-INDEX(Parameters!$J$13:$N$13,1,R85))*U85,INDEX(Parameters!$D$13:$H$13,1,R85)+(INDEX(Parameters!$D$13:$H$13,1,R85+1)-INDEX(Parameters!$D$13:$H$13,1,R85))*U85)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R85)+(INDEX(Parameters!$D$14:$H$14,1,R85+1)-INDEX(Parameters!$D$14:$H$14,1,R85))*U85)</f>
-        <v>0.57999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="L85" s="8">
         <f>I85+J85</f>
-        <v>1460</v>
+        <v>2008</v>
       </c>
       <c r="M85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S85)+(INDEX(Parameters!$J$17:$N$17,1,S85+1)-INDEX(Parameters!$J$17:$N$17,1,S85))*V85,INDEX(Parameters!$D$17:$H$17,1,S85)+(INDEX(Parameters!$D$17:$H$17,1,S85+1)-INDEX(Parameters!$D$17:$H$17,1,S85))*V85)</f>
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="N85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S85)+(INDEX(Parameters!$J$18:$N$18,1,S85+1)-INDEX(Parameters!$J$18:$N$18,1,S85))*V85,INDEX(Parameters!$D$18:$H$18,1,S85)+(INDEX(Parameters!$D$18:$H$18,1,S85+1)-INDEX(Parameters!$D$18:$H$18,1,S85))*V85)</f>
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="O85" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S85)+(INDEX(Parameters!$J$19:$N$19,1,S85+1)-INDEX(Parameters!$J$19:$N$19,1,S85))*V85,INDEX(Parameters!$D$19:$H$19,1,S85)+(INDEX(Parameters!$D$19:$H$19,1,S85+1)-INDEX(Parameters!$D$19:$H$19,1,S85))*V85)</f>
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="P85" s="8">
         <f>M85*O85</f>
-        <v>880</v>
+        <v>1056</v>
       </c>
       <c r="Q85" s="8">
         <f>MIN(4,MAX(1,INT((1+C85/Parameters!$D$23)*4)+1))</f>
@@ -14888,47 +14788,47 @@
       </c>
       <c r="F86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q86)+(INDEX(Parameters!$J$10:$N$10,1,Q86+1)-INDEX(Parameters!$J$10:$N$10,1,Q86))*T86,INDEX(Parameters!$D$10:$H$10,1,Q86)+(INDEX(Parameters!$D$10:$H$10,1,Q86+1)-INDEX(Parameters!$D$10:$H$10,1,Q86))*T86)</f>
-        <v>1750</v>
+        <v>2400</v>
       </c>
       <c r="G86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R86)+(INDEX(Parameters!$J$11:$N$11,1,R86+1)-INDEX(Parameters!$J$11:$N$11,1,R86))*U86,INDEX(Parameters!$D$11:$H$11,1,Q86)+(INDEX(Parameters!$D$11:$H$11,1,Q86+1)-INDEX(Parameters!$D$11:$H$11,1,Q86))*T86)</f>
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="H86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q86)+(INDEX(Parameters!$J$12:$N$12,1,Q86+1)-INDEX(Parameters!$J$12:$N$12,1,Q86))*T86,INDEX(Parameters!$D$12:$H$12,1,Q86)+(INDEX(Parameters!$D$12:$H$12,1,Q86+1)-INDEX(Parameters!$D$12:$H$12,1,Q86))*T86)</f>
-        <v>0.92999999999999994</v>
+        <v>0.54</v>
       </c>
       <c r="I86" s="8">
         <f>F86*H86</f>
-        <v>1627.5</v>
+        <v>1296</v>
       </c>
       <c r="J86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R86)+(INDEX(Parameters!$J$13:$N$13,1,R86+1)-INDEX(Parameters!$J$13:$N$13,1,R86))*U86,INDEX(Parameters!$D$13:$H$13,1,R86)+(INDEX(Parameters!$D$13:$H$13,1,R86+1)-INDEX(Parameters!$D$13:$H$13,1,R86))*U86)</f>
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="K86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R86)+(INDEX(Parameters!$D$14:$H$14,1,R86+1)-INDEX(Parameters!$D$14:$H$14,1,R86))*U86)</f>
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="L86" s="8">
         <f>I86+J86</f>
-        <v>2877.5</v>
+        <v>2296</v>
       </c>
       <c r="M86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S86)+(INDEX(Parameters!$J$17:$N$17,1,S86+1)-INDEX(Parameters!$J$17:$N$17,1,S86))*V86,INDEX(Parameters!$D$17:$H$17,1,S86)+(INDEX(Parameters!$D$17:$H$17,1,S86+1)-INDEX(Parameters!$D$17:$H$17,1,S86))*V86)</f>
-        <v>1500</v>
+        <v>2050</v>
       </c>
       <c r="N86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S86)+(INDEX(Parameters!$J$18:$N$18,1,S86+1)-INDEX(Parameters!$J$18:$N$18,1,S86))*V86,INDEX(Parameters!$D$18:$H$18,1,S86)+(INDEX(Parameters!$D$18:$H$18,1,S86+1)-INDEX(Parameters!$D$18:$H$18,1,S86))*V86)</f>
-        <v>0.255</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="O86" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S86)+(INDEX(Parameters!$J$19:$N$19,1,S86+1)-INDEX(Parameters!$J$19:$N$19,1,S86))*V86,INDEX(Parameters!$D$19:$H$19,1,S86)+(INDEX(Parameters!$D$19:$H$19,1,S86+1)-INDEX(Parameters!$D$19:$H$19,1,S86))*V86)</f>
-        <v>0.84000000000000008</v>
+        <v>0.62</v>
       </c>
       <c r="P86" s="8">
         <f>M86*O86</f>
-        <v>1260.0000000000002</v>
+        <v>1271</v>
       </c>
       <c r="Q86" s="8">
         <f>MIN(4,MAX(1,INT((1+C86/Parameters!$D$23)*4)+1))</f>
@@ -14974,23 +14874,23 @@
       </c>
       <c r="F87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q87)+(INDEX(Parameters!$J$10:$N$10,1,Q87+1)-INDEX(Parameters!$J$10:$N$10,1,Q87))*T87,INDEX(Parameters!$D$10:$H$10,1,Q87)+(INDEX(Parameters!$D$10:$H$10,1,Q87+1)-INDEX(Parameters!$D$10:$H$10,1,Q87))*T87)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R87)+(INDEX(Parameters!$J$11:$N$11,1,R87+1)-INDEX(Parameters!$J$11:$N$11,1,R87))*U87,INDEX(Parameters!$D$11:$H$11,1,Q87)+(INDEX(Parameters!$D$11:$H$11,1,Q87+1)-INDEX(Parameters!$D$11:$H$11,1,Q87))*T87)</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q87)+(INDEX(Parameters!$J$12:$N$12,1,Q87+1)-INDEX(Parameters!$J$12:$N$12,1,Q87))*T87,INDEX(Parameters!$D$12:$H$12,1,Q87)+(INDEX(Parameters!$D$12:$H$12,1,Q87+1)-INDEX(Parameters!$D$12:$H$12,1,Q87))*T87)</f>
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="I87" s="8">
         <f>F87*H87</f>
-        <v>2250</v>
+        <v>1560</v>
       </c>
       <c r="J87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R87)+(INDEX(Parameters!$J$13:$N$13,1,R87+1)-INDEX(Parameters!$J$13:$N$13,1,R87))*U87,INDEX(Parameters!$D$13:$H$13,1,R87)+(INDEX(Parameters!$D$13:$H$13,1,R87+1)-INDEX(Parameters!$D$13:$H$13,1,R87))*U87)</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="K87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R87)+(INDEX(Parameters!$D$14:$H$14,1,R87+1)-INDEX(Parameters!$D$14:$H$14,1,R87))*U87)</f>
@@ -14998,23 +14898,23 @@
       </c>
       <c r="L87" s="8">
         <f>I87+J87</f>
-        <v>4250</v>
+        <v>2560</v>
       </c>
       <c r="M87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S87)+(INDEX(Parameters!$J$17:$N$17,1,S87+1)-INDEX(Parameters!$J$17:$N$17,1,S87))*V87,INDEX(Parameters!$D$17:$H$17,1,S87)+(INDEX(Parameters!$D$17:$H$17,1,S87+1)-INDEX(Parameters!$D$17:$H$17,1,S87))*V87)</f>
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="N87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S87)+(INDEX(Parameters!$J$18:$N$18,1,S87+1)-INDEX(Parameters!$J$18:$N$18,1,S87))*V87,INDEX(Parameters!$D$18:$H$18,1,S87)+(INDEX(Parameters!$D$18:$H$18,1,S87+1)-INDEX(Parameters!$D$18:$H$18,1,S87))*V87)</f>
-        <v>0.28000000000000003</v>
+        <v>0.25</v>
       </c>
       <c r="O87" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S87)+(INDEX(Parameters!$J$19:$N$19,1,S87+1)-INDEX(Parameters!$J$19:$N$19,1,S87))*V87,INDEX(Parameters!$D$19:$H$19,1,S87)+(INDEX(Parameters!$D$19:$H$19,1,S87+1)-INDEX(Parameters!$D$19:$H$19,1,S87))*V87)</f>
-        <v>0.8</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P87" s="8">
         <f>M87*O87</f>
-        <v>1600</v>
+        <v>1450</v>
       </c>
       <c r="Q87" s="8">
         <f>MIN(4,MAX(1,INT((1+C87/Parameters!$D$23)*4)+1))</f>
@@ -15060,47 +14960,47 @@
       </c>
       <c r="F88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q88)+(INDEX(Parameters!$J$10:$N$10,1,Q88+1)-INDEX(Parameters!$J$10:$N$10,1,Q88))*T88,INDEX(Parameters!$D$10:$H$10,1,Q88)+(INDEX(Parameters!$D$10:$H$10,1,Q88+1)-INDEX(Parameters!$D$10:$H$10,1,Q88))*T88)</f>
-        <v>3250</v>
+        <v>3600</v>
       </c>
       <c r="G88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R88)+(INDEX(Parameters!$J$11:$N$11,1,R88+1)-INDEX(Parameters!$J$11:$N$11,1,R88))*U88,INDEX(Parameters!$D$11:$H$11,1,Q88)+(INDEX(Parameters!$D$11:$H$11,1,Q88+1)-INDEX(Parameters!$D$11:$H$11,1,Q88))*T88)</f>
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="H88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q88)+(INDEX(Parameters!$J$12:$N$12,1,Q88+1)-INDEX(Parameters!$J$12:$N$12,1,Q88))*T88,INDEX(Parameters!$D$12:$H$12,1,Q88)+(INDEX(Parameters!$D$12:$H$12,1,Q88+1)-INDEX(Parameters!$D$12:$H$12,1,Q88))*T88)</f>
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="I88" s="8">
         <f>F88*H88</f>
-        <v>2827.5</v>
+        <v>1800</v>
       </c>
       <c r="J88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R88)+(INDEX(Parameters!$J$13:$N$13,1,R88+1)-INDEX(Parameters!$J$13:$N$13,1,R88))*U88,INDEX(Parameters!$D$13:$H$13,1,R88)+(INDEX(Parameters!$D$13:$H$13,1,R88+1)-INDEX(Parameters!$D$13:$H$13,1,R88))*U88)</f>
-        <v>2750</v>
+        <v>1000</v>
       </c>
       <c r="K88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R88)+(INDEX(Parameters!$D$14:$H$14,1,R88+1)-INDEX(Parameters!$D$14:$H$14,1,R88))*U88)</f>
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="L88" s="8">
         <f>I88+J88</f>
-        <v>5577.5</v>
+        <v>2800</v>
       </c>
       <c r="M88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S88)+(INDEX(Parameters!$J$17:$N$17,1,S88+1)-INDEX(Parameters!$J$17:$N$17,1,S88))*V88,INDEX(Parameters!$D$17:$H$17,1,S88)+(INDEX(Parameters!$D$17:$H$17,1,S88+1)-INDEX(Parameters!$D$17:$H$17,1,S88))*V88)</f>
-        <v>2500</v>
+        <v>2950</v>
       </c>
       <c r="N88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S88)+(INDEX(Parameters!$J$18:$N$18,1,S88+1)-INDEX(Parameters!$J$18:$N$18,1,S88))*V88,INDEX(Parameters!$D$18:$H$18,1,S88)+(INDEX(Parameters!$D$18:$H$18,1,S88+1)-INDEX(Parameters!$D$18:$H$18,1,S88))*V88)</f>
-        <v>0.30500000000000005</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="O88" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S88)+(INDEX(Parameters!$J$19:$N$19,1,S88+1)-INDEX(Parameters!$J$19:$N$19,1,S88))*V88,INDEX(Parameters!$D$19:$H$19,1,S88)+(INDEX(Parameters!$D$19:$H$19,1,S88+1)-INDEX(Parameters!$D$19:$H$19,1,S88))*V88)</f>
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="P88" s="8">
         <f>M88*O88</f>
-        <v>1900</v>
+        <v>1593</v>
       </c>
       <c r="Q88" s="8">
         <f>MIN(4,MAX(1,INT((1+C88/Parameters!$D$23)*4)+1))</f>
@@ -15146,47 +15046,47 @@
       </c>
       <c r="F89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q89)+(INDEX(Parameters!$J$10:$N$10,1,Q89+1)-INDEX(Parameters!$J$10:$N$10,1,Q89))*T89,INDEX(Parameters!$D$10:$H$10,1,Q89)+(INDEX(Parameters!$D$10:$H$10,1,Q89+1)-INDEX(Parameters!$D$10:$H$10,1,Q89))*T89)</f>
-        <v>4000</v>
+        <v>4200</v>
       </c>
       <c r="G89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R89)+(INDEX(Parameters!$J$11:$N$11,1,R89+1)-INDEX(Parameters!$J$11:$N$11,1,R89))*U89,INDEX(Parameters!$D$11:$H$11,1,Q89)+(INDEX(Parameters!$D$11:$H$11,1,Q89+1)-INDEX(Parameters!$D$11:$H$11,1,Q89))*T89)</f>
-        <v>0.12</v>
+        <v>0.45</v>
       </c>
       <c r="H89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q89)+(INDEX(Parameters!$J$12:$N$12,1,Q89+1)-INDEX(Parameters!$J$12:$N$12,1,Q89))*T89,INDEX(Parameters!$D$12:$H$12,1,Q89)+(INDEX(Parameters!$D$12:$H$12,1,Q89+1)-INDEX(Parameters!$D$12:$H$12,1,Q89))*T89)</f>
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="I89" s="8">
         <f>F89*H89</f>
-        <v>3360</v>
+        <v>2016</v>
       </c>
       <c r="J89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R89)+(INDEX(Parameters!$J$13:$N$13,1,R89+1)-INDEX(Parameters!$J$13:$N$13,1,R89))*U89,INDEX(Parameters!$D$13:$H$13,1,R89)+(INDEX(Parameters!$D$13:$H$13,1,R89+1)-INDEX(Parameters!$D$13:$H$13,1,R89))*U89)</f>
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="K89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R89)+(INDEX(Parameters!$D$14:$H$14,1,R89+1)-INDEX(Parameters!$D$14:$H$14,1,R89))*U89)</f>
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="L89" s="8">
         <f>I89+J89</f>
-        <v>6860</v>
+        <v>3016</v>
       </c>
       <c r="M89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S89)+(INDEX(Parameters!$J$17:$N$17,1,S89+1)-INDEX(Parameters!$J$17:$N$17,1,S89))*V89,INDEX(Parameters!$D$17:$H$17,1,S89)+(INDEX(Parameters!$D$17:$H$17,1,S89+1)-INDEX(Parameters!$D$17:$H$17,1,S89))*V89)</f>
-        <v>3000</v>
+        <v>3400</v>
       </c>
       <c r="N89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S89)+(INDEX(Parameters!$J$18:$N$18,1,S89+1)-INDEX(Parameters!$J$18:$N$18,1,S89))*V89,INDEX(Parameters!$D$18:$H$18,1,S89)+(INDEX(Parameters!$D$18:$H$18,1,S89+1)-INDEX(Parameters!$D$18:$H$18,1,S89))*V89)</f>
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O89" s="8">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S89)+(INDEX(Parameters!$J$19:$N$19,1,S89+1)-INDEX(Parameters!$J$19:$N$19,1,S89))*V89,INDEX(Parameters!$D$19:$H$19,1,S89)+(INDEX(Parameters!$D$19:$H$19,1,S89+1)-INDEX(Parameters!$D$19:$H$19,1,S89))*V89)</f>
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="P89" s="8">
         <f>M89*O89</f>
-        <v>2160</v>
+        <v>1700</v>
       </c>
       <c r="Q89" s="8">
         <f>MIN(4,MAX(1,INT((1+C89/Parameters!$D$23)*4)+1))</f>
@@ -15284,7 +15184,7 @@
     </row>
     <row r="93" spans="2:22" ht="22" customHeight="1">
       <c r="B93" s="11" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C93" s="11" t="str">
         <f>B85</f>
@@ -15368,23 +15268,23 @@
       </c>
       <c r="C95" s="15">
         <f t="shared" si="10"/>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D95" s="15">
         <f t="shared" si="11"/>
-        <v>75</v>
+        <v>102.5</v>
       </c>
       <c r="E95" s="15">
         <f t="shared" si="12"/>
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F95" s="15">
         <f t="shared" si="13"/>
-        <v>125</v>
+        <v>147.5</v>
       </c>
       <c r="G95" s="15">
         <f t="shared" si="14"/>
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="H95" s="8"/>
       <c r="I95" s="8"/>
@@ -15408,23 +15308,23 @@
       </c>
       <c r="C96" s="15">
         <f t="shared" si="10"/>
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="D96" s="15">
         <f t="shared" si="11"/>
-        <v>150</v>
+        <v>205</v>
       </c>
       <c r="E96" s="15">
         <f t="shared" si="12"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F96" s="15">
         <f t="shared" si="13"/>
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="G96" s="15">
         <f t="shared" si="14"/>
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
@@ -15448,23 +15348,23 @@
       </c>
       <c r="C97" s="15">
         <f t="shared" si="10"/>
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="D97" s="15">
         <f t="shared" si="11"/>
-        <v>225</v>
+        <v>307.5</v>
       </c>
       <c r="E97" s="15">
         <f t="shared" si="12"/>
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="F97" s="15">
         <f t="shared" si="13"/>
-        <v>375</v>
+        <v>442.5</v>
       </c>
       <c r="G97" s="15">
         <f t="shared" si="14"/>
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="H97" s="8"/>
       <c r="I97" s="8"/>
@@ -15488,23 +15388,23 @@
       </c>
       <c r="C98" s="15">
         <f t="shared" si="10"/>
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="D98" s="15">
         <f t="shared" si="11"/>
-        <v>300</v>
+        <v>410</v>
       </c>
       <c r="E98" s="15">
         <f t="shared" si="12"/>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F98" s="15">
         <f t="shared" si="13"/>
-        <v>500</v>
+        <v>590</v>
       </c>
       <c r="G98" s="15">
         <f t="shared" si="14"/>
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="H98" s="8"/>
       <c r="I98" s="8"/>
@@ -15528,23 +15428,23 @@
       </c>
       <c r="C99" s="15">
         <f t="shared" si="10"/>
-        <v>247.6</v>
+        <v>372.8</v>
       </c>
       <c r="D99" s="15">
         <f t="shared" si="11"/>
-        <v>375</v>
+        <v>493.02499999999998</v>
       </c>
       <c r="E99" s="15">
         <f t="shared" si="12"/>
-        <v>500</v>
+        <v>625</v>
       </c>
       <c r="F99" s="15">
         <f t="shared" si="13"/>
-        <v>625</v>
+        <v>737.5</v>
       </c>
       <c r="G99" s="15">
         <f t="shared" si="14"/>
-        <v>750</v>
+        <v>850</v>
       </c>
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
@@ -15568,23 +15468,23 @@
       </c>
       <c r="C100" s="15">
         <f t="shared" si="10"/>
-        <v>291.59999999999997</v>
+        <v>425.59999999999997</v>
       </c>
       <c r="D100" s="15">
         <f t="shared" si="11"/>
-        <v>439.2</v>
+        <v>556.57499999999993</v>
       </c>
       <c r="E100" s="15">
         <f t="shared" si="12"/>
-        <v>591.99999999999989</v>
+        <v>697.5</v>
       </c>
       <c r="F100" s="15">
         <f t="shared" si="13"/>
-        <v>750</v>
+        <v>851.07500000000005</v>
       </c>
       <c r="G100" s="15">
         <f t="shared" si="14"/>
-        <v>900</v>
+        <v>1020</v>
       </c>
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
@@ -15608,23 +15508,23 @@
       </c>
       <c r="C101" s="15">
         <f t="shared" si="10"/>
-        <v>335.59999999999997</v>
+        <v>478.4</v>
       </c>
       <c r="D101" s="15">
         <f t="shared" si="11"/>
-        <v>502.2</v>
+        <v>620.125</v>
       </c>
       <c r="E101" s="15">
         <f t="shared" si="12"/>
-        <v>671.99999999999989</v>
+        <v>770</v>
       </c>
       <c r="F101" s="15">
         <f t="shared" si="13"/>
-        <v>848</v>
+        <v>930.72500000000002</v>
       </c>
       <c r="G101" s="15">
         <f t="shared" si="14"/>
-        <v>1033.1999999999998</v>
+        <v>1105</v>
       </c>
       <c r="H101" s="8"/>
       <c r="I101" s="8"/>
@@ -15648,23 +15548,23 @@
       </c>
       <c r="C102" s="15">
         <f t="shared" si="10"/>
-        <v>379.6</v>
+        <v>531.20000000000005</v>
       </c>
       <c r="D102" s="15">
         <f t="shared" si="11"/>
-        <v>565.20000000000005</v>
+        <v>683.67499999999995</v>
       </c>
       <c r="E102" s="15">
         <f t="shared" si="12"/>
-        <v>752</v>
+        <v>842.5</v>
       </c>
       <c r="F102" s="15">
         <f t="shared" si="13"/>
-        <v>943</v>
+        <v>1010.3750000000001</v>
       </c>
       <c r="G102" s="15">
         <f t="shared" si="14"/>
-        <v>1141.2</v>
+        <v>1190</v>
       </c>
       <c r="H102" s="8"/>
       <c r="I102" s="8"/>
@@ -15688,23 +15588,23 @@
       </c>
       <c r="C103" s="15">
         <f t="shared" si="10"/>
-        <v>423.6</v>
+        <v>584</v>
       </c>
       <c r="D103" s="15">
         <f t="shared" si="11"/>
-        <v>628.20000000000005</v>
+        <v>747.22500000000002</v>
       </c>
       <c r="E103" s="15">
         <f t="shared" si="12"/>
-        <v>832</v>
+        <v>915</v>
       </c>
       <c r="F103" s="15">
         <f t="shared" si="13"/>
-        <v>1038</v>
+        <v>1090.0250000000001</v>
       </c>
       <c r="G103" s="15">
         <f t="shared" si="14"/>
-        <v>1249.2</v>
+        <v>1275</v>
       </c>
       <c r="H103" s="8"/>
       <c r="I103" s="8"/>
@@ -15728,23 +15628,23 @@
       </c>
       <c r="C104" s="15">
         <f t="shared" si="10"/>
-        <v>467.6</v>
+        <v>636.79999999999995</v>
       </c>
       <c r="D104" s="15">
         <f t="shared" si="11"/>
-        <v>691.2</v>
+        <v>810.77500000000009</v>
       </c>
       <c r="E104" s="15">
         <f t="shared" si="12"/>
-        <v>912</v>
+        <v>987.5</v>
       </c>
       <c r="F104" s="15">
         <f t="shared" si="13"/>
-        <v>1133</v>
+        <v>1169.6750000000002</v>
       </c>
       <c r="G104" s="15">
         <f t="shared" si="14"/>
-        <v>1357.2</v>
+        <v>1360</v>
       </c>
       <c r="H104" s="8"/>
       <c r="I104" s="8"/>
@@ -15768,23 +15668,23 @@
       </c>
       <c r="C105" s="15">
         <f t="shared" si="10"/>
-        <v>511.60000000000008</v>
+        <v>689.6</v>
       </c>
       <c r="D105" s="15">
         <f t="shared" si="11"/>
-        <v>754.2</v>
+        <v>874.32500000000005</v>
       </c>
       <c r="E105" s="15">
         <f t="shared" si="12"/>
-        <v>992</v>
+        <v>1060</v>
       </c>
       <c r="F105" s="15">
         <f t="shared" si="13"/>
-        <v>1228</v>
+        <v>1249.3250000000003</v>
       </c>
       <c r="G105" s="15">
         <f t="shared" si="14"/>
-        <v>1465.2</v>
+        <v>1445</v>
       </c>
       <c r="H105" s="8"/>
       <c r="I105" s="8"/>
@@ -15808,23 +15708,23 @@
       </c>
       <c r="C106" s="15">
         <f t="shared" si="10"/>
-        <v>555.6</v>
+        <v>742.4</v>
       </c>
       <c r="D106" s="15">
         <f t="shared" si="11"/>
-        <v>817.2</v>
+        <v>937.875</v>
       </c>
       <c r="E106" s="15">
         <f t="shared" si="12"/>
-        <v>1072</v>
+        <v>1132.5</v>
       </c>
       <c r="F106" s="15">
         <f t="shared" si="13"/>
-        <v>1323</v>
+        <v>1328.9749999999999</v>
       </c>
       <c r="G106" s="15">
         <f t="shared" si="14"/>
-        <v>1573.1999999999998</v>
+        <v>1530</v>
       </c>
       <c r="H106" s="8"/>
       <c r="I106" s="8"/>
@@ -15848,23 +15748,23 @@
       </c>
       <c r="C107" s="15">
         <f t="shared" si="10"/>
-        <v>599.6</v>
+        <v>795.2</v>
       </c>
       <c r="D107" s="15">
         <f t="shared" si="11"/>
-        <v>880.2</v>
+        <v>1001.4250000000001</v>
       </c>
       <c r="E107" s="15">
         <f t="shared" si="12"/>
-        <v>1152</v>
+        <v>1205</v>
       </c>
       <c r="F107" s="15">
         <f t="shared" si="13"/>
-        <v>1418</v>
+        <v>1408.625</v>
       </c>
       <c r="G107" s="15">
         <f t="shared" si="14"/>
-        <v>1681.2</v>
+        <v>1615</v>
       </c>
       <c r="H107" s="8"/>
       <c r="I107" s="8"/>
@@ -15888,23 +15788,23 @@
       </c>
       <c r="C108" s="15">
         <f t="shared" si="10"/>
-        <v>643.59999999999991</v>
+        <v>847.99999999999989</v>
       </c>
       <c r="D108" s="15">
         <f t="shared" si="11"/>
-        <v>943.2</v>
+        <v>1064.9749999999999</v>
       </c>
       <c r="E108" s="15">
         <f t="shared" si="12"/>
-        <v>1232</v>
+        <v>1277.5</v>
       </c>
       <c r="F108" s="15">
         <f t="shared" si="13"/>
-        <v>1513</v>
+        <v>1488.2750000000001</v>
       </c>
       <c r="G108" s="15">
         <f t="shared" si="14"/>
-        <v>1789.1999999999998</v>
+        <v>1700</v>
       </c>
       <c r="H108" s="8"/>
       <c r="I108" s="8"/>
@@ -15928,23 +15828,23 @@
       </c>
       <c r="C109" s="15">
         <f t="shared" si="10"/>
-        <v>687.6</v>
+        <v>900.80000000000007</v>
       </c>
       <c r="D109" s="15">
         <f t="shared" si="11"/>
-        <v>1006.2000000000002</v>
+        <v>1128.5250000000001</v>
       </c>
       <c r="E109" s="15">
         <f t="shared" si="12"/>
-        <v>1312</v>
+        <v>1350</v>
       </c>
       <c r="F109" s="15">
         <f t="shared" si="13"/>
-        <v>1608</v>
+        <v>1567.9250000000002</v>
       </c>
       <c r="G109" s="15">
         <f t="shared" si="14"/>
-        <v>1897.1999999999998</v>
+        <v>1785</v>
       </c>
       <c r="H109" s="8"/>
       <c r="I109" s="8"/>
@@ -15968,23 +15868,23 @@
       </c>
       <c r="C110" s="15">
         <f t="shared" si="10"/>
-        <v>731.60000000000014</v>
+        <v>953.60000000000014</v>
       </c>
       <c r="D110" s="15">
         <f t="shared" si="11"/>
-        <v>1069.2000000000003</v>
+        <v>1192.075</v>
       </c>
       <c r="E110" s="15">
         <f t="shared" si="12"/>
-        <v>1392</v>
+        <v>1422.5</v>
       </c>
       <c r="F110" s="15">
         <f t="shared" si="13"/>
-        <v>1703</v>
+        <v>1647.5750000000003</v>
       </c>
       <c r="G110" s="15">
         <f t="shared" si="14"/>
-        <v>2005.2</v>
+        <v>1870</v>
       </c>
       <c r="H110" s="8"/>
       <c r="I110" s="8"/>
@@ -16008,23 +15908,23 @@
       </c>
       <c r="C111" s="15">
         <f t="shared" si="10"/>
-        <v>775.6</v>
+        <v>1006.3999999999999</v>
       </c>
       <c r="D111" s="15">
         <f t="shared" si="11"/>
-        <v>1132.2</v>
+        <v>1255.625</v>
       </c>
       <c r="E111" s="15">
         <f t="shared" si="12"/>
-        <v>1472</v>
+        <v>1495</v>
       </c>
       <c r="F111" s="15">
         <f t="shared" si="13"/>
-        <v>1798</v>
+        <v>1727.2249999999999</v>
       </c>
       <c r="G111" s="15">
         <f t="shared" si="14"/>
-        <v>2113.1999999999998</v>
+        <v>1955</v>
       </c>
       <c r="H111" s="8"/>
       <c r="I111" s="8"/>
@@ -16048,23 +15948,23 @@
       </c>
       <c r="C112" s="15">
         <f t="shared" si="10"/>
-        <v>819.6</v>
+        <v>1059.1999999999998</v>
       </c>
       <c r="D112" s="15">
         <f t="shared" si="11"/>
-        <v>1195.2000000000003</v>
+        <v>1319.1750000000002</v>
       </c>
       <c r="E112" s="15">
         <f t="shared" si="12"/>
-        <v>1552</v>
+        <v>1567.5</v>
       </c>
       <c r="F112" s="15">
         <f t="shared" si="13"/>
-        <v>1893</v>
+        <v>1806.875</v>
       </c>
       <c r="G112" s="15">
         <f t="shared" si="14"/>
-        <v>2221.1999999999998</v>
+        <v>2040</v>
       </c>
       <c r="H112" s="8"/>
       <c r="I112" s="8"/>
@@ -16088,23 +15988,23 @@
       </c>
       <c r="C113" s="15">
         <f t="shared" si="10"/>
-        <v>863.6</v>
+        <v>1112</v>
       </c>
       <c r="D113" s="15">
         <f t="shared" si="11"/>
-        <v>1258.2</v>
+        <v>1382.7249999999999</v>
       </c>
       <c r="E113" s="15">
         <f t="shared" si="12"/>
-        <v>1632</v>
+        <v>1640</v>
       </c>
       <c r="F113" s="15">
         <f t="shared" si="13"/>
-        <v>1988</v>
+        <v>1886.5250000000001</v>
       </c>
       <c r="G113" s="15">
         <f t="shared" si="14"/>
-        <v>2329.1999999999998</v>
+        <v>2125</v>
       </c>
       <c r="H113" s="8"/>
       <c r="I113" s="8"/>
@@ -16128,23 +16028,23 @@
       </c>
       <c r="C114" s="15">
         <f t="shared" si="10"/>
-        <v>907.6</v>
+        <v>1164.8000000000002</v>
       </c>
       <c r="D114" s="15">
         <f t="shared" si="11"/>
-        <v>1321.2000000000003</v>
+        <v>1446.2750000000001</v>
       </c>
       <c r="E114" s="15">
         <f t="shared" si="12"/>
-        <v>1712</v>
+        <v>1712.5</v>
       </c>
       <c r="F114" s="15">
         <f t="shared" si="13"/>
-        <v>2083</v>
+        <v>1966.1750000000002</v>
       </c>
       <c r="G114" s="15">
         <f t="shared" si="14"/>
-        <v>2437.1999999999998</v>
+        <v>2210</v>
       </c>
       <c r="H114" s="8"/>
       <c r="I114" s="8"/>
@@ -16302,7 +16202,7 @@
     </row>
     <row r="121" spans="2:22" ht="22" customHeight="1">
       <c r="B121" s="29" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="C121" s="29"/>
       <c r="D121" s="29"/>
@@ -16373,67 +16273,67 @@
     </row>
     <row r="124" spans="2:22" ht="35" customHeight="1">
       <c r="B124" s="13" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="C124" s="13" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E124" s="13" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F124" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G124" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H124" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I124" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J124" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K124" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="L124" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="M124" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="N124" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G124" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H124" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="I124" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="J124" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="K124" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="L124" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="M124" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="N124" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="O124" s="13" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="P124" s="13" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="Q124" s="13" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="R124" s="13" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="S124" s="13" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="T124" s="13" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="U124" s="13" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="V124" s="13" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="125" spans="2:22" ht="22" customHeight="1">
@@ -16455,7 +16355,7 @@
       </c>
       <c r="F125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q125)+(INDEX(Parameters!$J$10:$N$10,1,Q125+1)-INDEX(Parameters!$J$10:$N$10,1,Q125))*T125,INDEX(Parameters!$D$10:$H$10,1,Q125)+(INDEX(Parameters!$D$10:$H$10,1,Q125+1)-INDEX(Parameters!$D$10:$H$10,1,Q125))*T125)</f>
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="G125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R125)+(INDEX(Parameters!$J$11:$N$11,1,R125+1)-INDEX(Parameters!$J$11:$N$11,1,R125))*U125,INDEX(Parameters!$D$11:$H$11,1,Q125)+(INDEX(Parameters!$D$11:$H$11,1,Q125+1)-INDEX(Parameters!$D$11:$H$11,1,Q125))*T125)</f>
@@ -16463,15 +16363,15 @@
       </c>
       <c r="H125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q125)+(INDEX(Parameters!$J$12:$N$12,1,Q125+1)-INDEX(Parameters!$J$12:$N$12,1,Q125))*T125,INDEX(Parameters!$D$12:$H$12,1,Q125)+(INDEX(Parameters!$D$12:$H$12,1,Q125+1)-INDEX(Parameters!$D$12:$H$12,1,Q125))*T125)</f>
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I125" s="8">
         <f>F125*H125</f>
-        <v>960</v>
+        <v>1200</v>
       </c>
       <c r="J125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R125)+(INDEX(Parameters!$J$13:$N$13,1,R125+1)-INDEX(Parameters!$J$13:$N$13,1,R125))*U125,INDEX(Parameters!$D$13:$H$13,1,R125)+(INDEX(Parameters!$D$13:$H$13,1,R125+1)-INDEX(Parameters!$D$13:$H$13,1,R125))*U125)</f>
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="K125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R125)+(INDEX(Parameters!$D$14:$H$14,1,R125+1)-INDEX(Parameters!$D$14:$H$14,1,R125))*U125)</f>
@@ -16479,11 +16379,11 @@
       </c>
       <c r="L125" s="8">
         <f>I125+J125</f>
-        <v>1460</v>
+        <v>2000</v>
       </c>
       <c r="M125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S125)+(INDEX(Parameters!$J$17:$N$17,1,S125+1)-INDEX(Parameters!$J$17:$N$17,1,S125))*V125,INDEX(Parameters!$D$17:$H$17,1,S125)+(INDEX(Parameters!$D$17:$H$17,1,S125+1)-INDEX(Parameters!$D$17:$H$17,1,S125))*V125)</f>
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="N125" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S125)+(INDEX(Parameters!$J$18:$N$18,1,S125+1)-INDEX(Parameters!$J$18:$N$18,1,S125))*V125,INDEX(Parameters!$D$18:$H$18,1,S125)+(INDEX(Parameters!$D$18:$H$18,1,S125+1)-INDEX(Parameters!$D$18:$H$18,1,S125))*V125)</f>
@@ -16495,7 +16395,7 @@
       </c>
       <c r="P125" s="8">
         <f>M125*O125</f>
-        <v>880</v>
+        <v>968</v>
       </c>
       <c r="Q125" s="8">
         <f>MIN(4,MAX(1,INT((1+C125/Parameters!$D$23)*4)+1))</f>
@@ -16541,7 +16441,7 @@
       </c>
       <c r="F126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q126)+(INDEX(Parameters!$J$10:$N$10,1,Q126+1)-INDEX(Parameters!$J$10:$N$10,1,Q126))*T126,INDEX(Parameters!$D$10:$H$10,1,Q126)+(INDEX(Parameters!$D$10:$H$10,1,Q126+1)-INDEX(Parameters!$D$10:$H$10,1,Q126))*T126)</f>
-        <v>1750</v>
+        <v>1800</v>
       </c>
       <c r="G126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R126)+(INDEX(Parameters!$J$11:$N$11,1,R126+1)-INDEX(Parameters!$J$11:$N$11,1,R126))*U126,INDEX(Parameters!$D$11:$H$11,1,Q126)+(INDEX(Parameters!$D$11:$H$11,1,Q126+1)-INDEX(Parameters!$D$11:$H$11,1,Q126))*T126)</f>
@@ -16549,15 +16449,15 @@
       </c>
       <c r="H126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q126)+(INDEX(Parameters!$J$12:$N$12,1,Q126+1)-INDEX(Parameters!$J$12:$N$12,1,Q126))*T126,INDEX(Parameters!$D$12:$H$12,1,Q126)+(INDEX(Parameters!$D$12:$H$12,1,Q126+1)-INDEX(Parameters!$D$12:$H$12,1,Q126))*T126)</f>
-        <v>0.92999999999999994</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I126" s="8">
         <f>F126*H126</f>
-        <v>1627.5</v>
+        <v>1755</v>
       </c>
       <c r="J126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R126)+(INDEX(Parameters!$J$13:$N$13,1,R126+1)-INDEX(Parameters!$J$13:$N$13,1,R126))*U126,INDEX(Parameters!$D$13:$H$13,1,R126)+(INDEX(Parameters!$D$13:$H$13,1,R126+1)-INDEX(Parameters!$D$13:$H$13,1,R126))*U126)</f>
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="K126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R126)+(INDEX(Parameters!$D$14:$H$14,1,R126+1)-INDEX(Parameters!$D$14:$H$14,1,R126))*U126)</f>
@@ -16565,11 +16465,11 @@
       </c>
       <c r="L126" s="8">
         <f>I126+J126</f>
-        <v>2877.5</v>
+        <v>3155</v>
       </c>
       <c r="M126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S126)+(INDEX(Parameters!$J$17:$N$17,1,S126+1)-INDEX(Parameters!$J$17:$N$17,1,S126))*V126,INDEX(Parameters!$D$17:$H$17,1,S126)+(INDEX(Parameters!$D$17:$H$17,1,S126+1)-INDEX(Parameters!$D$17:$H$17,1,S126))*V126)</f>
-        <v>1500</v>
+        <v>1550</v>
       </c>
       <c r="N126" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S126)+(INDEX(Parameters!$J$18:$N$18,1,S126+1)-INDEX(Parameters!$J$18:$N$18,1,S126))*V126,INDEX(Parameters!$D$18:$H$18,1,S126)+(INDEX(Parameters!$D$18:$H$18,1,S126+1)-INDEX(Parameters!$D$18:$H$18,1,S126))*V126)</f>
@@ -16581,7 +16481,7 @@
       </c>
       <c r="P126" s="8">
         <f>M126*O126</f>
-        <v>1260.0000000000002</v>
+        <v>1302.0000000000002</v>
       </c>
       <c r="Q126" s="8">
         <f>MIN(4,MAX(1,INT((1+C126/Parameters!$D$23)*4)+1))</f>
@@ -16627,7 +16527,7 @@
       </c>
       <c r="F127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q127)+(INDEX(Parameters!$J$10:$N$10,1,Q127+1)-INDEX(Parameters!$J$10:$N$10,1,Q127))*T127,INDEX(Parameters!$D$10:$H$10,1,Q127)+(INDEX(Parameters!$D$10:$H$10,1,Q127+1)-INDEX(Parameters!$D$10:$H$10,1,Q127))*T127)</f>
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="G127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R127)+(INDEX(Parameters!$J$11:$N$11,1,R127+1)-INDEX(Parameters!$J$11:$N$11,1,R127))*U127,INDEX(Parameters!$D$11:$H$11,1,Q127)+(INDEX(Parameters!$D$11:$H$11,1,Q127+1)-INDEX(Parameters!$D$11:$H$11,1,Q127))*T127)</f>
@@ -16635,11 +16535,11 @@
       </c>
       <c r="H127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q127)+(INDEX(Parameters!$J$12:$N$12,1,Q127+1)-INDEX(Parameters!$J$12:$N$12,1,Q127))*T127,INDEX(Parameters!$D$12:$H$12,1,Q127)+(INDEX(Parameters!$D$12:$H$12,1,Q127+1)-INDEX(Parameters!$D$12:$H$12,1,Q127))*T127)</f>
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I127" s="8">
         <f>F127*H127</f>
-        <v>2250</v>
+        <v>2280</v>
       </c>
       <c r="J127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R127)+(INDEX(Parameters!$J$13:$N$13,1,R127+1)-INDEX(Parameters!$J$13:$N$13,1,R127))*U127,INDEX(Parameters!$D$13:$H$13,1,R127)+(INDEX(Parameters!$D$13:$H$13,1,R127+1)-INDEX(Parameters!$D$13:$H$13,1,R127))*U127)</f>
@@ -16651,7 +16551,7 @@
       </c>
       <c r="L127" s="8">
         <f>I127+J127</f>
-        <v>4250</v>
+        <v>4280</v>
       </c>
       <c r="M127" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S127)+(INDEX(Parameters!$J$17:$N$17,1,S127+1)-INDEX(Parameters!$J$17:$N$17,1,S127))*V127,INDEX(Parameters!$D$17:$H$17,1,S127)+(INDEX(Parameters!$D$17:$H$17,1,S127+1)-INDEX(Parameters!$D$17:$H$17,1,S127))*V127)</f>
@@ -16713,7 +16613,7 @@
       </c>
       <c r="F128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q128)+(INDEX(Parameters!$J$10:$N$10,1,Q128+1)-INDEX(Parameters!$J$10:$N$10,1,Q128))*T128,INDEX(Parameters!$D$10:$H$10,1,Q128)+(INDEX(Parameters!$D$10:$H$10,1,Q128+1)-INDEX(Parameters!$D$10:$H$10,1,Q128))*T128)</f>
-        <v>3250</v>
+        <v>3000</v>
       </c>
       <c r="G128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R128)+(INDEX(Parameters!$J$11:$N$11,1,R128+1)-INDEX(Parameters!$J$11:$N$11,1,R128))*U128,INDEX(Parameters!$D$11:$H$11,1,Q128)+(INDEX(Parameters!$D$11:$H$11,1,Q128+1)-INDEX(Parameters!$D$11:$H$11,1,Q128))*T128)</f>
@@ -16721,15 +16621,15 @@
       </c>
       <c r="H128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q128)+(INDEX(Parameters!$J$12:$N$12,1,Q128+1)-INDEX(Parameters!$J$12:$N$12,1,Q128))*T128,INDEX(Parameters!$D$12:$H$12,1,Q128)+(INDEX(Parameters!$D$12:$H$12,1,Q128+1)-INDEX(Parameters!$D$12:$H$12,1,Q128))*T128)</f>
-        <v>0.87</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="I128" s="8">
         <f>F128*H128</f>
-        <v>2827.5</v>
+        <v>2775</v>
       </c>
       <c r="J128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R128)+(INDEX(Parameters!$J$13:$N$13,1,R128+1)-INDEX(Parameters!$J$13:$N$13,1,R128))*U128,INDEX(Parameters!$D$13:$H$13,1,R128)+(INDEX(Parameters!$D$13:$H$13,1,R128+1)-INDEX(Parameters!$D$13:$H$13,1,R128))*U128)</f>
-        <v>2750</v>
+        <v>2600</v>
       </c>
       <c r="K128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R128)+(INDEX(Parameters!$D$14:$H$14,1,R128+1)-INDEX(Parameters!$D$14:$H$14,1,R128))*U128)</f>
@@ -16737,11 +16637,11 @@
       </c>
       <c r="L128" s="8">
         <f>I128+J128</f>
-        <v>5577.5</v>
+        <v>5375</v>
       </c>
       <c r="M128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S128)+(INDEX(Parameters!$J$17:$N$17,1,S128+1)-INDEX(Parameters!$J$17:$N$17,1,S128))*V128,INDEX(Parameters!$D$17:$H$17,1,S128)+(INDEX(Parameters!$D$17:$H$17,1,S128+1)-INDEX(Parameters!$D$17:$H$17,1,S128))*V128)</f>
-        <v>2500</v>
+        <v>2450</v>
       </c>
       <c r="N128" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S128)+(INDEX(Parameters!$J$18:$N$18,1,S128+1)-INDEX(Parameters!$J$18:$N$18,1,S128))*V128,INDEX(Parameters!$D$18:$H$18,1,S128)+(INDEX(Parameters!$D$18:$H$18,1,S128+1)-INDEX(Parameters!$D$18:$H$18,1,S128))*V128)</f>
@@ -16753,7 +16653,7 @@
       </c>
       <c r="P128" s="8">
         <f>M128*O128</f>
-        <v>1900</v>
+        <v>1862</v>
       </c>
       <c r="Q128" s="8">
         <f>MIN(4,MAX(1,INT((1+C128/Parameters!$D$23)*4)+1))</f>
@@ -16799,7 +16699,7 @@
       </c>
       <c r="F129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q129)+(INDEX(Parameters!$J$10:$N$10,1,Q129+1)-INDEX(Parameters!$J$10:$N$10,1,Q129))*T129,INDEX(Parameters!$D$10:$H$10,1,Q129)+(INDEX(Parameters!$D$10:$H$10,1,Q129+1)-INDEX(Parameters!$D$10:$H$10,1,Q129))*T129)</f>
-        <v>4000</v>
+        <v>3600</v>
       </c>
       <c r="G129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R129)+(INDEX(Parameters!$J$11:$N$11,1,R129+1)-INDEX(Parameters!$J$11:$N$11,1,R129))*U129,INDEX(Parameters!$D$11:$H$11,1,Q129)+(INDEX(Parameters!$D$11:$H$11,1,Q129+1)-INDEX(Parameters!$D$11:$H$11,1,Q129))*T129)</f>
@@ -16807,15 +16707,15 @@
       </c>
       <c r="H129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q129)+(INDEX(Parameters!$J$12:$N$12,1,Q129+1)-INDEX(Parameters!$J$12:$N$12,1,Q129))*T129,INDEX(Parameters!$D$12:$H$12,1,Q129)+(INDEX(Parameters!$D$12:$H$12,1,Q129+1)-INDEX(Parameters!$D$12:$H$12,1,Q129))*T129)</f>
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="I129" s="8">
         <f>F129*H129</f>
-        <v>3360</v>
+        <v>3240</v>
       </c>
       <c r="J129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R129)+(INDEX(Parameters!$J$13:$N$13,1,R129+1)-INDEX(Parameters!$J$13:$N$13,1,R129))*U129,INDEX(Parameters!$D$13:$H$13,1,R129)+(INDEX(Parameters!$D$13:$H$13,1,R129+1)-INDEX(Parameters!$D$13:$H$13,1,R129))*U129)</f>
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="K129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R129)+(INDEX(Parameters!$D$14:$H$14,1,R129+1)-INDEX(Parameters!$D$14:$H$14,1,R129))*U129)</f>
@@ -16823,11 +16723,11 @@
       </c>
       <c r="L129" s="8">
         <f>I129+J129</f>
-        <v>6860</v>
+        <v>6440</v>
       </c>
       <c r="M129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S129)+(INDEX(Parameters!$J$17:$N$17,1,S129+1)-INDEX(Parameters!$J$17:$N$17,1,S129))*V129,INDEX(Parameters!$D$17:$H$17,1,S129)+(INDEX(Parameters!$D$17:$H$17,1,S129+1)-INDEX(Parameters!$D$17:$H$17,1,S129))*V129)</f>
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="N129" s="8">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S129)+(INDEX(Parameters!$J$18:$N$18,1,S129+1)-INDEX(Parameters!$J$18:$N$18,1,S129))*V129,INDEX(Parameters!$D$18:$H$18,1,S129)+(INDEX(Parameters!$D$18:$H$18,1,S129+1)-INDEX(Parameters!$D$18:$H$18,1,S129))*V129)</f>
@@ -16839,7 +16739,7 @@
       </c>
       <c r="P129" s="8">
         <f>M129*O129</f>
-        <v>2160</v>
+        <v>2088</v>
       </c>
       <c r="Q129" s="8">
         <f>MIN(4,MAX(1,INT((1+C129/Parameters!$D$23)*4)+1))</f>
@@ -16937,7 +16837,7 @@
     </row>
     <row r="133" spans="2:22" ht="22" customHeight="1">
       <c r="B133" s="11" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C133" s="11" t="str">
         <f>B125</f>
@@ -17051,31 +16951,31 @@
       </c>
       <c r="C135" s="15">
         <f t="shared" si="15"/>
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D135" s="15">
         <f t="shared" si="16"/>
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="E135" s="15">
         <f t="shared" si="17"/>
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F135" s="15">
         <f t="shared" si="18"/>
-        <v>162.5</v>
+        <v>150</v>
       </c>
       <c r="G135" s="15">
         <f t="shared" si="19"/>
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H135" s="15">
         <f t="shared" si="20"/>
-        <v>-50</v>
+        <v>-55</v>
       </c>
       <c r="I135" s="15">
         <f t="shared" si="21"/>
-        <v>-75</v>
+        <v>-77.5</v>
       </c>
       <c r="J135" s="15">
         <f t="shared" si="22"/>
@@ -17083,11 +16983,11 @@
       </c>
       <c r="K135" s="15">
         <f t="shared" si="23"/>
-        <v>-125</v>
+        <v>-122.5</v>
       </c>
       <c r="L135" s="15">
         <f t="shared" si="24"/>
-        <v>-150</v>
+        <v>-145</v>
       </c>
       <c r="M135" s="8"/>
       <c r="N135" s="8"/>
@@ -17106,31 +17006,31 @@
       </c>
       <c r="C136" s="15">
         <f t="shared" si="15"/>
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D136" s="15">
         <f t="shared" si="16"/>
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E136" s="15">
         <f t="shared" si="17"/>
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="F136" s="15">
         <f t="shared" si="18"/>
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="G136" s="15">
         <f t="shared" si="19"/>
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="H136" s="15">
         <f t="shared" si="20"/>
-        <v>-100</v>
+        <v>-110</v>
       </c>
       <c r="I136" s="15">
         <f t="shared" si="21"/>
-        <v>-150</v>
+        <v>-155</v>
       </c>
       <c r="J136" s="15">
         <f t="shared" si="22"/>
@@ -17138,11 +17038,11 @@
       </c>
       <c r="K136" s="15">
         <f t="shared" si="23"/>
-        <v>-250</v>
+        <v>-245</v>
       </c>
       <c r="L136" s="15">
         <f t="shared" si="24"/>
-        <v>-300</v>
+        <v>-290</v>
       </c>
       <c r="M136" s="8"/>
       <c r="N136" s="8"/>
@@ -17161,31 +17061,31 @@
       </c>
       <c r="C137" s="15">
         <f t="shared" si="15"/>
-        <v>148.80000000000001</v>
+        <v>180</v>
       </c>
       <c r="D137" s="15">
         <f t="shared" si="16"/>
-        <v>258.82499999999999</v>
+        <v>268.64999999999998</v>
       </c>
       <c r="E137" s="15">
         <f t="shared" si="17"/>
-        <v>367.5</v>
+        <v>356.4</v>
       </c>
       <c r="F137" s="15">
         <f t="shared" si="18"/>
-        <v>474.82499999999999</v>
+        <v>443.25</v>
       </c>
       <c r="G137" s="15">
         <f t="shared" si="19"/>
-        <v>580.79999999999995</v>
+        <v>529.20000000000005</v>
       </c>
       <c r="H137" s="15">
         <f t="shared" si="20"/>
-        <v>-150</v>
+        <v>-165</v>
       </c>
       <c r="I137" s="15">
         <f t="shared" si="21"/>
-        <v>-225</v>
+        <v>-232.5</v>
       </c>
       <c r="J137" s="15">
         <f t="shared" si="22"/>
@@ -17193,11 +17093,11 @@
       </c>
       <c r="K137" s="15">
         <f t="shared" si="23"/>
-        <v>-375</v>
+        <v>-367.5</v>
       </c>
       <c r="L137" s="15">
         <f t="shared" si="24"/>
-        <v>-450</v>
+        <v>-435</v>
       </c>
       <c r="M137" s="8"/>
       <c r="N137" s="8"/>
@@ -17216,31 +17116,31 @@
       </c>
       <c r="C138" s="15">
         <f t="shared" si="15"/>
-        <v>196.8</v>
+        <v>240</v>
       </c>
       <c r="D138" s="15">
         <f t="shared" si="16"/>
-        <v>340.20000000000005</v>
+        <v>356.40000000000003</v>
       </c>
       <c r="E138" s="15">
         <f t="shared" si="17"/>
-        <v>480</v>
+        <v>470.40000000000003</v>
       </c>
       <c r="F138" s="15">
         <f t="shared" si="18"/>
-        <v>616.20000000000005</v>
+        <v>582</v>
       </c>
       <c r="G138" s="15">
         <f t="shared" si="19"/>
-        <v>748.80000000000007</v>
+        <v>691.2</v>
       </c>
       <c r="H138" s="15">
         <f t="shared" si="20"/>
-        <v>-200</v>
+        <v>-220</v>
       </c>
       <c r="I138" s="15">
         <f t="shared" si="21"/>
-        <v>-300</v>
+        <v>-310</v>
       </c>
       <c r="J138" s="15">
         <f t="shared" si="22"/>
@@ -17248,11 +17148,11 @@
       </c>
       <c r="K138" s="15">
         <f t="shared" si="23"/>
-        <v>-500</v>
+        <v>-490</v>
       </c>
       <c r="L138" s="15">
         <f t="shared" si="24"/>
-        <v>-600</v>
+        <v>-580</v>
       </c>
       <c r="M138" s="8"/>
       <c r="N138" s="8"/>
@@ -17271,31 +17171,31 @@
       </c>
       <c r="C139" s="15">
         <f t="shared" si="15"/>
-        <v>244.8</v>
+        <v>300</v>
       </c>
       <c r="D139" s="15">
         <f t="shared" si="16"/>
-        <v>421.57500000000005</v>
+        <v>444.15</v>
       </c>
       <c r="E139" s="15">
         <f t="shared" si="17"/>
-        <v>592.5</v>
+        <v>584.40000000000009</v>
       </c>
       <c r="F139" s="15">
         <f t="shared" si="18"/>
-        <v>757.57500000000005</v>
+        <v>720.75</v>
       </c>
       <c r="G139" s="15">
         <f t="shared" si="19"/>
-        <v>916.8</v>
+        <v>853.2</v>
       </c>
       <c r="H139" s="15">
         <f t="shared" si="20"/>
-        <v>-247.6</v>
+        <v>-272.36</v>
       </c>
       <c r="I139" s="15">
         <f t="shared" si="21"/>
-        <v>-375</v>
+        <v>-387.5</v>
       </c>
       <c r="J139" s="15">
         <f t="shared" si="22"/>
@@ -17303,11 +17203,11 @@
       </c>
       <c r="K139" s="15">
         <f t="shared" si="23"/>
-        <v>-625</v>
+        <v>-612.5</v>
       </c>
       <c r="L139" s="15">
         <f t="shared" si="24"/>
-        <v>-750</v>
+        <v>-725</v>
       </c>
       <c r="M139" s="8"/>
       <c r="N139" s="8"/>
@@ -17326,31 +17226,31 @@
       </c>
       <c r="C140" s="15">
         <f t="shared" si="15"/>
-        <v>292.79999999999995</v>
+        <v>360</v>
       </c>
       <c r="D140" s="15">
         <f t="shared" si="16"/>
-        <v>502.95</v>
+        <v>531.9</v>
       </c>
       <c r="E140" s="15">
         <f t="shared" si="17"/>
-        <v>705</v>
+        <v>698.4</v>
       </c>
       <c r="F140" s="15">
         <f t="shared" si="18"/>
-        <v>898.95</v>
+        <v>859.5</v>
       </c>
       <c r="G140" s="15">
         <f t="shared" si="19"/>
-        <v>1084.8</v>
+        <v>1015.1999999999999</v>
       </c>
       <c r="H140" s="15">
         <f t="shared" si="20"/>
-        <v>-291.59999999999997</v>
+        <v>-320.76</v>
       </c>
       <c r="I140" s="15">
         <f t="shared" si="21"/>
-        <v>-439.2</v>
+        <v>-453.84</v>
       </c>
       <c r="J140" s="15">
         <f t="shared" si="22"/>
@@ -17358,11 +17258,11 @@
       </c>
       <c r="K140" s="15">
         <f t="shared" si="23"/>
-        <v>-750</v>
+        <v>-735</v>
       </c>
       <c r="L140" s="15">
         <f t="shared" si="24"/>
-        <v>-900</v>
+        <v>-870</v>
       </c>
       <c r="M140" s="8"/>
       <c r="N140" s="8"/>
@@ -17381,31 +17281,31 @@
       </c>
       <c r="C141" s="15">
         <f t="shared" si="15"/>
-        <v>340.79999999999995</v>
+        <v>420</v>
       </c>
       <c r="D141" s="15">
         <f t="shared" si="16"/>
-        <v>584.32500000000005</v>
+        <v>619.65</v>
       </c>
       <c r="E141" s="15">
         <f t="shared" si="17"/>
-        <v>817.5</v>
+        <v>812.4</v>
       </c>
       <c r="F141" s="15">
         <f t="shared" si="18"/>
-        <v>1040.3249999999998</v>
+        <v>998.25</v>
       </c>
       <c r="G141" s="15">
         <f t="shared" si="19"/>
-        <v>1252.8</v>
+        <v>1177.1999999999998</v>
       </c>
       <c r="H141" s="15">
         <f t="shared" si="20"/>
-        <v>-335.59999999999997</v>
+        <v>-369.15999999999997</v>
       </c>
       <c r="I141" s="15">
         <f t="shared" si="21"/>
-        <v>-502.2</v>
+        <v>-518.93999999999994</v>
       </c>
       <c r="J141" s="15">
         <f t="shared" si="22"/>
@@ -17413,11 +17313,11 @@
       </c>
       <c r="K141" s="15">
         <f t="shared" si="23"/>
-        <v>-848</v>
+        <v>-831.04</v>
       </c>
       <c r="L141" s="15">
         <f t="shared" si="24"/>
-        <v>-1033.1999999999998</v>
+        <v>-998.75999999999988</v>
       </c>
       <c r="M141" s="8"/>
       <c r="N141" s="8"/>
@@ -17436,31 +17336,31 @@
       </c>
       <c r="C142" s="15">
         <f t="shared" si="15"/>
-        <v>388.8</v>
+        <v>480.00000000000006</v>
       </c>
       <c r="D142" s="15">
         <f t="shared" si="16"/>
-        <v>665.7</v>
+        <v>707.40000000000009</v>
       </c>
       <c r="E142" s="15">
         <f t="shared" si="17"/>
-        <v>930.00000000000011</v>
+        <v>926.40000000000009</v>
       </c>
       <c r="F142" s="15">
         <f t="shared" si="18"/>
-        <v>1181.7</v>
+        <v>1137</v>
       </c>
       <c r="G142" s="15">
         <f t="shared" si="19"/>
-        <v>1420.8000000000002</v>
+        <v>1339.2</v>
       </c>
       <c r="H142" s="15">
         <f t="shared" si="20"/>
-        <v>-379.6</v>
+        <v>-417.56</v>
       </c>
       <c r="I142" s="15">
         <f t="shared" si="21"/>
-        <v>-565.20000000000005</v>
+        <v>-584.04000000000008</v>
       </c>
       <c r="J142" s="15">
         <f t="shared" si="22"/>
@@ -17468,11 +17368,11 @@
       </c>
       <c r="K142" s="15">
         <f t="shared" si="23"/>
-        <v>-943</v>
+        <v>-924.1400000000001</v>
       </c>
       <c r="L142" s="15">
         <f t="shared" si="24"/>
-        <v>-1141.2</v>
+        <v>-1103.1600000000001</v>
       </c>
       <c r="M142" s="8"/>
       <c r="N142" s="8"/>
@@ -17491,31 +17391,31 @@
       </c>
       <c r="C143" s="15">
         <f t="shared" si="15"/>
-        <v>436.8</v>
+        <v>540</v>
       </c>
       <c r="D143" s="15">
         <f t="shared" si="16"/>
-        <v>747.07500000000005</v>
+        <v>795.15</v>
       </c>
       <c r="E143" s="15">
         <f t="shared" si="17"/>
-        <v>1042.5</v>
+        <v>1040.4000000000001</v>
       </c>
       <c r="F143" s="15">
         <f t="shared" si="18"/>
-        <v>1323.075</v>
+        <v>1275.75</v>
       </c>
       <c r="G143" s="15">
         <f t="shared" si="19"/>
-        <v>1588.8</v>
+        <v>1501.2</v>
       </c>
       <c r="H143" s="15">
         <f t="shared" si="20"/>
-        <v>-423.6</v>
+        <v>-465.96000000000004</v>
       </c>
       <c r="I143" s="15">
         <f t="shared" si="21"/>
-        <v>-628.20000000000005</v>
+        <v>-649.1400000000001</v>
       </c>
       <c r="J143" s="15">
         <f t="shared" si="22"/>
@@ -17523,11 +17423,11 @@
       </c>
       <c r="K143" s="15">
         <f t="shared" si="23"/>
-        <v>-1038</v>
+        <v>-1017.24</v>
       </c>
       <c r="L143" s="15">
         <f t="shared" si="24"/>
-        <v>-1249.2</v>
+        <v>-1207.56</v>
       </c>
       <c r="M143" s="8"/>
       <c r="N143" s="8"/>
@@ -17546,31 +17446,31 @@
       </c>
       <c r="C144" s="15">
         <f t="shared" si="15"/>
-        <v>484.8</v>
+        <v>600</v>
       </c>
       <c r="D144" s="15">
         <f t="shared" si="16"/>
-        <v>828.45</v>
+        <v>882.9</v>
       </c>
       <c r="E144" s="15">
         <f t="shared" si="17"/>
-        <v>1155</v>
+        <v>1154.4000000000001</v>
       </c>
       <c r="F144" s="15">
         <f t="shared" si="18"/>
-        <v>1464.45</v>
+        <v>1414.5</v>
       </c>
       <c r="G144" s="15">
         <f t="shared" si="19"/>
-        <v>1756.8</v>
+        <v>1663.2</v>
       </c>
       <c r="H144" s="15">
         <f t="shared" si="20"/>
-        <v>-467.6</v>
+        <v>-514.36</v>
       </c>
       <c r="I144" s="15">
         <f t="shared" si="21"/>
-        <v>-691.2</v>
+        <v>-714.24</v>
       </c>
       <c r="J144" s="15">
         <f t="shared" si="22"/>
@@ -17578,11 +17478,11 @@
       </c>
       <c r="K144" s="15">
         <f t="shared" si="23"/>
-        <v>-1133</v>
+        <v>-1110.3400000000001</v>
       </c>
       <c r="L144" s="15">
         <f t="shared" si="24"/>
-        <v>-1357.2</v>
+        <v>-1311.96</v>
       </c>
       <c r="M144" s="8"/>
       <c r="N144" s="8"/>
@@ -17601,31 +17501,31 @@
       </c>
       <c r="C145" s="15">
         <f t="shared" si="15"/>
-        <v>532.80000000000007</v>
+        <v>660.00000000000011</v>
       </c>
       <c r="D145" s="15">
         <f t="shared" si="16"/>
-        <v>909.82500000000005</v>
+        <v>970.65000000000009</v>
       </c>
       <c r="E145" s="15">
         <f t="shared" si="17"/>
-        <v>1267.5</v>
+        <v>1268.4000000000001</v>
       </c>
       <c r="F145" s="15">
         <f t="shared" si="18"/>
-        <v>1605.825</v>
+        <v>1553.2500000000002</v>
       </c>
       <c r="G145" s="15">
         <f t="shared" si="19"/>
-        <v>1924.8000000000002</v>
+        <v>1825.2</v>
       </c>
       <c r="H145" s="15">
         <f t="shared" si="20"/>
-        <v>-511.60000000000008</v>
+        <v>-562.76</v>
       </c>
       <c r="I145" s="15">
         <f t="shared" si="21"/>
-        <v>-754.2</v>
+        <v>-779.34000000000015</v>
       </c>
       <c r="J145" s="15">
         <f t="shared" si="22"/>
@@ -17633,11 +17533,11 @@
       </c>
       <c r="K145" s="15">
         <f t="shared" si="23"/>
-        <v>-1228</v>
+        <v>-1203.44</v>
       </c>
       <c r="L145" s="15">
         <f t="shared" si="24"/>
-        <v>-1465.2</v>
+        <v>-1416.3600000000001</v>
       </c>
       <c r="M145" s="8"/>
       <c r="N145" s="8"/>
@@ -17656,31 +17556,31 @@
       </c>
       <c r="C146" s="15">
         <f t="shared" si="15"/>
-        <v>590.79999999999995</v>
+        <v>736</v>
       </c>
       <c r="D146" s="15">
         <f t="shared" si="16"/>
-        <v>1003.6999999999999</v>
+        <v>1072.4000000000001</v>
       </c>
       <c r="E146" s="15">
         <f t="shared" si="17"/>
-        <v>1380</v>
+        <v>1382.3999999999999</v>
       </c>
       <c r="F146" s="15">
         <f t="shared" si="18"/>
-        <v>1747.2</v>
+        <v>1692</v>
       </c>
       <c r="G146" s="15">
         <f t="shared" si="19"/>
-        <v>2092.8000000000002</v>
+        <v>1987.2</v>
       </c>
       <c r="H146" s="15">
         <f t="shared" si="20"/>
-        <v>-555.6</v>
+        <v>-611.16</v>
       </c>
       <c r="I146" s="15">
         <f t="shared" si="21"/>
-        <v>-817.2</v>
+        <v>-844.44</v>
       </c>
       <c r="J146" s="15">
         <f t="shared" si="22"/>
@@ -17688,11 +17588,11 @@
       </c>
       <c r="K146" s="15">
         <f t="shared" si="23"/>
-        <v>-1323</v>
+        <v>-1296.54</v>
       </c>
       <c r="L146" s="15">
         <f t="shared" si="24"/>
-        <v>-1573.1999999999998</v>
+        <v>-1520.7599999999998</v>
       </c>
       <c r="M146" s="8"/>
       <c r="N146" s="8"/>
@@ -17711,31 +17611,31 @@
       </c>
       <c r="C147" s="15">
         <f t="shared" si="15"/>
-        <v>663.8</v>
+        <v>836</v>
       </c>
       <c r="D147" s="15">
         <f t="shared" si="16"/>
-        <v>1147.575</v>
+        <v>1230.1500000000001</v>
       </c>
       <c r="E147" s="15">
         <f t="shared" si="17"/>
-        <v>1592.5</v>
+        <v>1596.4</v>
       </c>
       <c r="F147" s="15">
         <f t="shared" si="18"/>
-        <v>1998.575</v>
+        <v>1934.75</v>
       </c>
       <c r="G147" s="15">
         <f t="shared" si="19"/>
-        <v>2365.8000000000002</v>
+        <v>2245.1999999999998</v>
       </c>
       <c r="H147" s="15">
         <f t="shared" si="20"/>
-        <v>-599.6</v>
+        <v>-659.56000000000006</v>
       </c>
       <c r="I147" s="15">
         <f t="shared" si="21"/>
-        <v>-880.2</v>
+        <v>-909.54000000000008</v>
       </c>
       <c r="J147" s="15">
         <f t="shared" si="22"/>
@@ -17743,11 +17643,11 @@
       </c>
       <c r="K147" s="15">
         <f t="shared" si="23"/>
-        <v>-1418</v>
+        <v>-1389.64</v>
       </c>
       <c r="L147" s="15">
         <f t="shared" si="24"/>
-        <v>-1681.2</v>
+        <v>-1625.1599999999999</v>
       </c>
       <c r="M147" s="8"/>
       <c r="N147" s="8"/>
@@ -17766,31 +17666,31 @@
       </c>
       <c r="C148" s="15">
         <f t="shared" si="15"/>
-        <v>736.8</v>
+        <v>936</v>
       </c>
       <c r="D148" s="15">
         <f t="shared" si="16"/>
-        <v>1291.4499999999998</v>
+        <v>1387.9</v>
       </c>
       <c r="E148" s="15">
         <f t="shared" si="17"/>
-        <v>1805</v>
+        <v>1810.3999999999999</v>
       </c>
       <c r="F148" s="15">
         <f t="shared" si="18"/>
-        <v>2277.4499999999998</v>
+        <v>2203.5</v>
       </c>
       <c r="G148" s="15">
         <f t="shared" si="19"/>
-        <v>2708.8</v>
+        <v>2567.1999999999998</v>
       </c>
       <c r="H148" s="15">
         <f t="shared" si="20"/>
-        <v>-643.59999999999991</v>
+        <v>-707.96</v>
       </c>
       <c r="I148" s="15">
         <f t="shared" si="21"/>
-        <v>-943.2</v>
+        <v>-974.64</v>
       </c>
       <c r="J148" s="15">
         <f t="shared" si="22"/>
@@ -17798,11 +17698,11 @@
       </c>
       <c r="K148" s="15">
         <f t="shared" si="23"/>
-        <v>-1513</v>
+        <v>-1482.7399999999998</v>
       </c>
       <c r="L148" s="15">
         <f t="shared" si="24"/>
-        <v>-1789.1999999999998</v>
+        <v>-1729.56</v>
       </c>
       <c r="M148" s="8"/>
       <c r="N148" s="8"/>
@@ -17821,31 +17721,31 @@
       </c>
       <c r="C149" s="15">
         <f t="shared" si="15"/>
-        <v>809.8</v>
+        <v>1036</v>
       </c>
       <c r="D149" s="15">
         <f t="shared" si="16"/>
-        <v>1435.325</v>
+        <v>1545.65</v>
       </c>
       <c r="E149" s="15">
         <f t="shared" si="17"/>
-        <v>2017.5</v>
+        <v>2024.4</v>
       </c>
       <c r="F149" s="15">
         <f t="shared" si="18"/>
-        <v>2556.3249999999998</v>
+        <v>2472.25</v>
       </c>
       <c r="G149" s="15">
         <f t="shared" si="19"/>
-        <v>3051.8</v>
+        <v>2889.2</v>
       </c>
       <c r="H149" s="15">
         <f t="shared" si="20"/>
-        <v>-687.6</v>
+        <v>-756.36</v>
       </c>
       <c r="I149" s="15">
         <f t="shared" si="21"/>
-        <v>-1006.2000000000002</v>
+        <v>-1039.7400000000002</v>
       </c>
       <c r="J149" s="15">
         <f t="shared" si="22"/>
@@ -17853,11 +17753,11 @@
       </c>
       <c r="K149" s="15">
         <f t="shared" si="23"/>
-        <v>-1608</v>
+        <v>-1575.8400000000001</v>
       </c>
       <c r="L149" s="15">
         <f t="shared" si="24"/>
-        <v>-1897.1999999999998</v>
+        <v>-1833.96</v>
       </c>
       <c r="M149" s="8"/>
       <c r="N149" s="8"/>
@@ -17876,31 +17776,31 @@
       </c>
       <c r="C150" s="15">
         <f t="shared" si="15"/>
-        <v>882.80000000000007</v>
+        <v>1136.0000000000002</v>
       </c>
       <c r="D150" s="15">
         <f t="shared" si="16"/>
-        <v>1579.2000000000003</v>
+        <v>1703.4</v>
       </c>
       <c r="E150" s="15">
         <f t="shared" si="17"/>
-        <v>2230</v>
+        <v>2238.4</v>
       </c>
       <c r="F150" s="15">
         <f t="shared" si="18"/>
-        <v>2835.2</v>
+        <v>2741</v>
       </c>
       <c r="G150" s="15">
         <f t="shared" si="19"/>
-        <v>3394.8</v>
+        <v>3211.2000000000003</v>
       </c>
       <c r="H150" s="15">
         <f t="shared" si="20"/>
-        <v>-731.60000000000014</v>
+        <v>-804.7600000000001</v>
       </c>
       <c r="I150" s="15">
         <f t="shared" si="21"/>
-        <v>-1069.2000000000003</v>
+        <v>-1104.8400000000001</v>
       </c>
       <c r="J150" s="15">
         <f t="shared" si="22"/>
@@ -17908,11 +17808,11 @@
       </c>
       <c r="K150" s="15">
         <f t="shared" si="23"/>
-        <v>-1703</v>
+        <v>-1668.94</v>
       </c>
       <c r="L150" s="15">
         <f t="shared" si="24"/>
-        <v>-2005.2</v>
+        <v>-1938.3600000000001</v>
       </c>
       <c r="M150" s="8"/>
       <c r="N150" s="8"/>
@@ -17931,31 +17831,31 @@
       </c>
       <c r="C151" s="15">
         <f t="shared" si="15"/>
-        <v>955.8</v>
+        <v>1236</v>
       </c>
       <c r="D151" s="15">
         <f t="shared" si="16"/>
-        <v>1723.075</v>
+        <v>1861.1499999999999</v>
       </c>
       <c r="E151" s="15">
         <f t="shared" si="17"/>
-        <v>2442.5</v>
+        <v>2452.3999999999996</v>
       </c>
       <c r="F151" s="15">
         <f t="shared" si="18"/>
-        <v>3114.0749999999998</v>
+        <v>3009.75</v>
       </c>
       <c r="G151" s="15">
         <f t="shared" si="19"/>
-        <v>3737.7999999999997</v>
+        <v>3533.2</v>
       </c>
       <c r="H151" s="15">
         <f t="shared" si="20"/>
-        <v>-775.6</v>
+        <v>-853.16</v>
       </c>
       <c r="I151" s="15">
         <f t="shared" si="21"/>
-        <v>-1132.2</v>
+        <v>-1169.94</v>
       </c>
       <c r="J151" s="15">
         <f t="shared" si="22"/>
@@ -17963,11 +17863,11 @@
       </c>
       <c r="K151" s="15">
         <f t="shared" si="23"/>
-        <v>-1798</v>
+        <v>-1762.04</v>
       </c>
       <c r="L151" s="15">
         <f t="shared" si="24"/>
-        <v>-2113.1999999999998</v>
+        <v>-2042.76</v>
       </c>
       <c r="M151" s="8"/>
       <c r="N151" s="8"/>
@@ -17986,31 +17886,31 @@
       </c>
       <c r="C152" s="15">
         <f t="shared" si="15"/>
-        <v>1028.8000000000002</v>
+        <v>1336</v>
       </c>
       <c r="D152" s="15">
         <f t="shared" si="16"/>
-        <v>1866.95</v>
+        <v>2018.9</v>
       </c>
       <c r="E152" s="15">
         <f t="shared" si="17"/>
-        <v>2655</v>
+        <v>2666.4</v>
       </c>
       <c r="F152" s="15">
         <f t="shared" si="18"/>
-        <v>3392.9500000000003</v>
+        <v>3278.5</v>
       </c>
       <c r="G152" s="15">
         <f t="shared" si="19"/>
-        <v>4080.8</v>
+        <v>3855.2000000000003</v>
       </c>
       <c r="H152" s="15">
         <f t="shared" si="20"/>
-        <v>-819.6</v>
+        <v>-901.56000000000006</v>
       </c>
       <c r="I152" s="15">
         <f t="shared" si="21"/>
-        <v>-1195.2000000000003</v>
+        <v>-1235.0400000000002</v>
       </c>
       <c r="J152" s="15">
         <f t="shared" si="22"/>
@@ -18018,11 +17918,11 @@
       </c>
       <c r="K152" s="15">
         <f t="shared" si="23"/>
-        <v>-1893</v>
+        <v>-1855.1399999999999</v>
       </c>
       <c r="L152" s="15">
         <f t="shared" si="24"/>
-        <v>-2221.1999999999998</v>
+        <v>-2147.16</v>
       </c>
       <c r="M152" s="8"/>
       <c r="N152" s="8"/>
@@ -18041,31 +17941,31 @@
       </c>
       <c r="C153" s="15">
         <f t="shared" si="15"/>
-        <v>1101.8</v>
+        <v>1436</v>
       </c>
       <c r="D153" s="15">
         <f t="shared" si="16"/>
-        <v>2010.825</v>
+        <v>2176.6499999999996</v>
       </c>
       <c r="E153" s="15">
         <f t="shared" si="17"/>
-        <v>2867.5</v>
+        <v>2880.3999999999996</v>
       </c>
       <c r="F153" s="15">
         <f t="shared" si="18"/>
-        <v>3671.8249999999998</v>
+        <v>3547.25</v>
       </c>
       <c r="G153" s="15">
         <f t="shared" si="19"/>
-        <v>4423.7999999999993</v>
+        <v>4177.2</v>
       </c>
       <c r="H153" s="15">
         <f t="shared" si="20"/>
-        <v>-863.6</v>
+        <v>-949.95999999999992</v>
       </c>
       <c r="I153" s="15">
         <f t="shared" si="21"/>
-        <v>-1258.2</v>
+        <v>-1300.1400000000001</v>
       </c>
       <c r="J153" s="15">
         <f t="shared" si="22"/>
@@ -18073,11 +17973,11 @@
       </c>
       <c r="K153" s="15">
         <f t="shared" si="23"/>
-        <v>-1988</v>
+        <v>-1948.2399999999998</v>
       </c>
       <c r="L153" s="15">
         <f t="shared" si="24"/>
-        <v>-2329.1999999999998</v>
+        <v>-2251.5599999999995</v>
       </c>
       <c r="M153" s="8"/>
       <c r="N153" s="8"/>
@@ -18096,31 +17996,31 @@
       </c>
       <c r="C154" s="15">
         <f t="shared" si="15"/>
-        <v>1174.8</v>
+        <v>1536</v>
       </c>
       <c r="D154" s="15">
         <f t="shared" si="16"/>
-        <v>2154.6999999999998</v>
+        <v>2334.4</v>
       </c>
       <c r="E154" s="15">
         <f t="shared" si="17"/>
-        <v>3080</v>
+        <v>3094.4</v>
       </c>
       <c r="F154" s="15">
         <f t="shared" si="18"/>
-        <v>3950.7</v>
+        <v>3816</v>
       </c>
       <c r="G154" s="15">
         <f t="shared" si="19"/>
-        <v>4766.8</v>
+        <v>4499.2</v>
       </c>
       <c r="H154" s="15">
         <f t="shared" si="20"/>
-        <v>-907.6</v>
+        <v>-998.36</v>
       </c>
       <c r="I154" s="15">
         <f t="shared" si="21"/>
-        <v>-1321.2000000000003</v>
+        <v>-1365.2400000000002</v>
       </c>
       <c r="J154" s="15">
         <f t="shared" si="22"/>
@@ -18128,11 +18028,11 @@
       </c>
       <c r="K154" s="15">
         <f t="shared" si="23"/>
-        <v>-2083</v>
+        <v>-2041.3400000000001</v>
       </c>
       <c r="L154" s="15">
         <f t="shared" si="24"/>
-        <v>-2437.1999999999998</v>
+        <v>-2355.96</v>
       </c>
       <c r="M154" s="8"/>
       <c r="N154" s="8"/>
@@ -18216,7 +18116,7 @@
     </row>
     <row r="161" spans="2:22">
       <c r="B161" s="30" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C161" s="30"/>
       <c r="D161" s="30"/>
@@ -18241,67 +18141,67 @@
     </row>
     <row r="164" spans="2:22">
       <c r="B164" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="C164" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D164" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E164" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F164" t="s">
+        <v>15</v>
+      </c>
+      <c r="G164" t="s">
+        <v>56</v>
+      </c>
+      <c r="H164" t="s">
+        <v>45</v>
+      </c>
+      <c r="I164" t="s">
+        <v>36</v>
+      </c>
+      <c r="J164" t="s">
+        <v>46</v>
+      </c>
+      <c r="K164" t="s">
+        <v>57</v>
+      </c>
+      <c r="L164" t="s">
+        <v>47</v>
+      </c>
+      <c r="M164" t="s">
+        <v>20</v>
+      </c>
+      <c r="N164" t="s">
         <v>21</v>
       </c>
-      <c r="G164" t="s">
-        <v>81</v>
-      </c>
-      <c r="H164" t="s">
-        <v>67</v>
-      </c>
-      <c r="I164" t="s">
-        <v>57</v>
-      </c>
-      <c r="J164" t="s">
-        <v>68</v>
-      </c>
-      <c r="K164" t="s">
-        <v>82</v>
-      </c>
-      <c r="L164" t="s">
-        <v>69</v>
-      </c>
-      <c r="M164" t="s">
-        <v>28</v>
-      </c>
-      <c r="N164" t="s">
-        <v>29</v>
-      </c>
       <c r="O164" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="P164" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="Q164" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="R164" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="S164" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="T164" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="U164" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="V164" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="165" spans="2:22">
@@ -18319,23 +18219,23 @@
       </c>
       <c r="F165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q165)+(INDEX(Parameters!$J$10:$N$10,1,Q165+1)-INDEX(Parameters!$J$10:$N$10,1,Q165))*T165,INDEX(Parameters!$D$10:$H$10,1,Q165)+(INDEX(Parameters!$D$10:$H$10,1,Q165+1)-INDEX(Parameters!$D$10:$H$10,1,Q165))*T165)</f>
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R165)+(INDEX(Parameters!$J$11:$N$11,1,R165+1)-INDEX(Parameters!$J$11:$N$11,1,R165))*U165,INDEX(Parameters!$D$11:$H$11,1,Q165)+(INDEX(Parameters!$D$11:$H$11,1,Q165+1)-INDEX(Parameters!$D$11:$H$11,1,Q165))*T165)</f>
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q165)+(INDEX(Parameters!$J$12:$N$12,1,Q165+1)-INDEX(Parameters!$J$12:$N$12,1,Q165))*T165,INDEX(Parameters!$D$12:$H$12,1,Q165)+(INDEX(Parameters!$D$12:$H$12,1,Q165+1)-INDEX(Parameters!$D$12:$H$12,1,Q165))*T165)</f>
-        <v>0.9</v>
+        <v>0.52</v>
       </c>
       <c r="I165">
         <f>F165*H165</f>
-        <v>2250</v>
+        <v>1560</v>
       </c>
       <c r="J165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R165)+(INDEX(Parameters!$J$13:$N$13,1,R165+1)-INDEX(Parameters!$J$13:$N$13,1,R165))*U165,INDEX(Parameters!$D$13:$H$13,1,R165)+(INDEX(Parameters!$D$13:$H$13,1,R165+1)-INDEX(Parameters!$D$13:$H$13,1,R165))*U165)</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="K165">
         <f>IF(Calculator!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R165)+(INDEX(Parameters!$D$14:$H$14,1,R165+1)-INDEX(Parameters!$D$14:$H$14,1,R165))*U165)</f>
@@ -18343,23 +18243,23 @@
       </c>
       <c r="L165">
         <f>I165+J165</f>
-        <v>4250</v>
+        <v>2560</v>
       </c>
       <c r="M165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S165)+(INDEX(Parameters!$J$17:$N$17,1,S165+1)-INDEX(Parameters!$J$17:$N$17,1,S165))*V165,INDEX(Parameters!$D$17:$H$17,1,S165)+(INDEX(Parameters!$D$17:$H$17,1,S165+1)-INDEX(Parameters!$D$17:$H$17,1,S165))*V165)</f>
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="N165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S165)+(INDEX(Parameters!$J$18:$N$18,1,S165+1)-INDEX(Parameters!$J$18:$N$18,1,S165))*V165,INDEX(Parameters!$D$18:$H$18,1,S165)+(INDEX(Parameters!$D$18:$H$18,1,S165+1)-INDEX(Parameters!$D$18:$H$18,1,S165))*V165)</f>
-        <v>0.28000000000000003</v>
+        <v>0.25</v>
       </c>
       <c r="O165">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S165)+(INDEX(Parameters!$J$19:$N$19,1,S165+1)-INDEX(Parameters!$J$19:$N$19,1,S165))*V165,INDEX(Parameters!$D$19:$H$19,1,S165)+(INDEX(Parameters!$D$19:$H$19,1,S165+1)-INDEX(Parameters!$D$19:$H$19,1,S165))*V165)</f>
-        <v>0.8</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="P165">
         <f>M165*O165</f>
-        <v>1600</v>
+        <v>1450</v>
       </c>
       <c r="Q165">
         <f>MIN(4,MAX(1,INT((1+C165/Parameters!$D$23)*4)+1))</f>
